--- a/research/traditional_assets/database/data/norway/norway_steel.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_steel.xlsx
@@ -1376,7 +1376,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1513,22 +1513,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08830218928668868</v>
+        <v>0.08814302447025796</v>
       </c>
       <c r="C2">
-        <v>272.3924927633188</v>
+        <v>270.1794877185625</v>
       </c>
       <c r="D2">
-        <v>266.9524927633188</v>
+        <v>267.5054877185625</v>
       </c>
       <c r="E2">
-        <v>-27.5</v>
+        <v>-24.734</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.766</v>
       </c>
       <c r="G2">
         <v>5.44</v>
@@ -1549,28 +1549,28 @@
         <v>45.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1391298</v>
       </c>
       <c r="N2">
-        <v>45.8</v>
+        <v>45.6608702</v>
       </c>
       <c r="O2">
-        <v>10.076</v>
+        <v>10.045391444</v>
       </c>
       <c r="P2">
-        <v>35.724</v>
+        <v>35.615478756</v>
       </c>
       <c r="Q2">
-        <v>52.324</v>
+        <v>52.215478756</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08830218928668868</v>
+        <v>0.08863705502046258</v>
       </c>
       <c r="T2">
-        <v>0.9815748103161359</v>
+        <v>0.9893084300337781</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>329.1890019248212</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1595,22 +1595,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08814302447025796</v>
+        <v>0.08798385965382724</v>
       </c>
       <c r="C3">
-        <v>270.1794877185625</v>
+        <v>267.9687784996095</v>
       </c>
       <c r="D3">
-        <v>267.5054877185625</v>
+        <v>268.0607784996095</v>
       </c>
       <c r="E3">
-        <v>-24.734</v>
+        <v>-21.968</v>
       </c>
       <c r="F3">
-        <v>2.766</v>
+        <v>5.532000000000001</v>
       </c>
       <c r="G3">
         <v>5.44</v>
@@ -1631,28 +1631,28 @@
         <v>45.8</v>
       </c>
       <c r="M3">
-        <v>0.1391298</v>
+        <v>0.2782596000000001</v>
       </c>
       <c r="N3">
-        <v>45.6608702</v>
+        <v>45.5217404</v>
       </c>
       <c r="O3">
-        <v>10.045391444</v>
+        <v>10.014782888</v>
       </c>
       <c r="P3">
-        <v>35.615478756</v>
+        <v>35.506957512</v>
       </c>
       <c r="Q3">
-        <v>52.215478756</v>
+        <v>52.106957512</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08863705502046258</v>
+        <v>0.08897875474880332</v>
       </c>
       <c r="T3">
-        <v>0.9893084300337781</v>
+        <v>0.9971998787252498</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>329.1890019248212</v>
+        <v>164.5945009624106</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1677,22 +1677,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08798385965382724</v>
+        <v>0.08782469483739652</v>
       </c>
       <c r="C4">
-        <v>267.9687784996095</v>
+        <v>265.7603794332995</v>
       </c>
       <c r="D4">
-        <v>268.0607784996095</v>
+        <v>268.6183794332995</v>
       </c>
       <c r="E4">
-        <v>-21.968</v>
+        <v>-19.202</v>
       </c>
       <c r="F4">
-        <v>5.532000000000001</v>
+        <v>8.298</v>
       </c>
       <c r="G4">
         <v>5.44</v>
@@ -1713,28 +1713,28 @@
         <v>45.8</v>
       </c>
       <c r="M4">
-        <v>0.2782596000000001</v>
+        <v>0.4173894</v>
       </c>
       <c r="N4">
-        <v>45.5217404</v>
+        <v>45.3826106</v>
       </c>
       <c r="O4">
-        <v>10.014782888</v>
+        <v>9.984174332</v>
       </c>
       <c r="P4">
-        <v>35.506957512</v>
+        <v>35.398436268</v>
       </c>
       <c r="Q4">
-        <v>52.106957512</v>
+        <v>51.998436268</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08897875474880332</v>
+        <v>0.08932749983236755</v>
       </c>
       <c r="T4">
-        <v>0.9971998787252498</v>
+        <v>1.00525403769902</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>164.5945009624106</v>
+        <v>109.7296673082738</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1759,22 +1759,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08782469483739652</v>
+        <v>0.08766553002096582</v>
       </c>
       <c r="C5">
-        <v>265.7603794332995</v>
+        <v>263.5543049659276</v>
       </c>
       <c r="D5">
-        <v>268.6183794332995</v>
+        <v>269.1783049659276</v>
       </c>
       <c r="E5">
-        <v>-19.202</v>
+        <v>-16.436</v>
       </c>
       <c r="F5">
-        <v>8.298</v>
+        <v>11.064</v>
       </c>
       <c r="G5">
         <v>5.44</v>
@@ -1795,28 +1795,28 @@
         <v>45.8</v>
       </c>
       <c r="M5">
-        <v>0.4173894</v>
+        <v>0.5565192000000001</v>
       </c>
       <c r="N5">
-        <v>45.3826106</v>
+        <v>45.2434808</v>
       </c>
       <c r="O5">
-        <v>9.984174332</v>
+        <v>9.953565776</v>
       </c>
       <c r="P5">
-        <v>35.398436268</v>
+        <v>35.289915024</v>
       </c>
       <c r="Q5">
-        <v>51.998436268</v>
+        <v>51.889915024</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08932749983236755</v>
+        <v>0.08968351043850606</v>
       </c>
       <c r="T5">
-        <v>1.00525403769902</v>
+        <v>1.01347599165141</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>109.7296673082738</v>
+        <v>82.29725048120531</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1841,22 +1841,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08766553002096582</v>
+        <v>0.0875063652045351</v>
       </c>
       <c r="C6">
-        <v>263.5543049659276</v>
+        <v>261.3505696644916</v>
       </c>
       <c r="D6">
-        <v>269.1783049659276</v>
+        <v>269.7405696644916</v>
       </c>
       <c r="E6">
-        <v>-16.436</v>
+        <v>-13.67</v>
       </c>
       <c r="F6">
-        <v>11.064</v>
+        <v>13.83</v>
       </c>
       <c r="G6">
         <v>5.44</v>
@@ -1877,28 +1877,28 @@
         <v>45.8</v>
       </c>
       <c r="M6">
-        <v>0.5565192000000001</v>
+        <v>0.6956490000000001</v>
       </c>
       <c r="N6">
-        <v>45.2434808</v>
+        <v>45.10435099999999</v>
       </c>
       <c r="O6">
-        <v>9.953565776</v>
+        <v>9.922957219999999</v>
       </c>
       <c r="P6">
-        <v>35.289915024</v>
+        <v>35.18139377999999</v>
       </c>
       <c r="Q6">
-        <v>51.889915024</v>
+        <v>51.78139377999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08968351043850606</v>
+        <v>0.0900470160047738</v>
       </c>
       <c r="T6">
-        <v>1.01347599165141</v>
+        <v>1.021871039371219</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>82.29725048120531</v>
+        <v>65.83780038496424</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1923,22 +1923,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0875063652045351</v>
+        <v>0.08734720038810438</v>
       </c>
       <c r="C7">
-        <v>261.3505696644916</v>
+        <v>259.1491882179552</v>
       </c>
       <c r="D7">
-        <v>269.7405696644916</v>
+        <v>270.3051882179552</v>
       </c>
       <c r="E7">
-        <v>-13.67</v>
+        <v>-10.904</v>
       </c>
       <c r="F7">
-        <v>13.83</v>
+        <v>16.596</v>
       </c>
       <c r="G7">
         <v>5.44</v>
@@ -1959,28 +1959,28 @@
         <v>45.8</v>
       </c>
       <c r="M7">
-        <v>0.6956490000000001</v>
+        <v>0.8347788000000002</v>
       </c>
       <c r="N7">
-        <v>45.10435099999999</v>
+        <v>44.96522119999999</v>
       </c>
       <c r="O7">
-        <v>9.922957219999999</v>
+        <v>9.892348663999998</v>
       </c>
       <c r="P7">
-        <v>35.18139377999999</v>
+        <v>35.072872536</v>
       </c>
       <c r="Q7">
-        <v>51.78139377999999</v>
+        <v>51.672872536</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0900470160047738</v>
+        <v>0.09041825573202594</v>
       </c>
       <c r="T7">
-        <v>1.021871039371219</v>
+        <v>1.03044470512762</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>65.83780038496424</v>
+        <v>54.86483365413687</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2005,22 +2005,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08734720038810438</v>
+        <v>0.08718803557167368</v>
       </c>
       <c r="C8">
-        <v>259.1491882179552</v>
+        <v>256.9501754385274</v>
       </c>
       <c r="D8">
-        <v>270.3051882179552</v>
+        <v>270.8721754385274</v>
       </c>
       <c r="E8">
-        <v>-10.904</v>
+        <v>-8.138000000000002</v>
       </c>
       <c r="F8">
-        <v>16.596</v>
+        <v>19.362</v>
       </c>
       <c r="G8">
         <v>5.44</v>
@@ -2041,28 +2041,28 @@
         <v>45.8</v>
       </c>
       <c r="M8">
-        <v>0.8347787999999999</v>
+        <v>0.9739085999999999</v>
       </c>
       <c r="N8">
-        <v>44.96522119999999</v>
+        <v>44.8260914</v>
       </c>
       <c r="O8">
-        <v>9.892348663999998</v>
+        <v>9.861740107999999</v>
       </c>
       <c r="P8">
-        <v>35.072872536</v>
+        <v>34.964351292</v>
       </c>
       <c r="Q8">
-        <v>51.672872536</v>
+        <v>51.564351292</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09041825573202594</v>
+        <v>0.09079747910932653</v>
       </c>
       <c r="T8">
-        <v>1.03044470512762</v>
+        <v>1.039202750792761</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>54.86483365413688</v>
+        <v>47.02700027497447</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2087,22 +2087,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08718803557167368</v>
+        <v>0.08702887075524296</v>
       </c>
       <c r="C9">
-        <v>256.9501754385274</v>
+        <v>254.7535462629577</v>
       </c>
       <c r="D9">
-        <v>270.8721754385274</v>
+        <v>271.4415462629577</v>
       </c>
       <c r="E9">
-        <v>-8.137999999999998</v>
+        <v>-5.371999999999996</v>
       </c>
       <c r="F9">
-        <v>19.362</v>
+        <v>22.128</v>
       </c>
       <c r="G9">
         <v>5.44</v>
@@ -2123,28 +2123,28 @@
         <v>45.8</v>
       </c>
       <c r="M9">
-        <v>0.9739086</v>
+        <v>1.1130384</v>
       </c>
       <c r="N9">
-        <v>44.8260914</v>
+        <v>44.6869616</v>
       </c>
       <c r="O9">
-        <v>9.861740107999999</v>
+        <v>9.831131551999999</v>
       </c>
       <c r="P9">
-        <v>34.964351292</v>
+        <v>34.855830048</v>
       </c>
       <c r="Q9">
-        <v>51.564351292</v>
+        <v>51.455830048</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09079747910932653</v>
+        <v>0.09118494647309017</v>
       </c>
       <c r="T9">
-        <v>1.039202750792761</v>
+        <v>1.048151188754969</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>47.02700027497446</v>
+        <v>41.14862524060265</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2169,22 +2169,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08702887075524296</v>
+        <v>0.08686970593881224</v>
       </c>
       <c r="C10">
-        <v>254.7535462629577</v>
+        <v>252.5593157538479</v>
       </c>
       <c r="D10">
-        <v>271.4415462629577</v>
+        <v>272.0133157538479</v>
       </c>
       <c r="E10">
-        <v>-5.371999999999996</v>
+        <v>-2.605999999999998</v>
       </c>
       <c r="F10">
-        <v>22.128</v>
+        <v>24.894</v>
       </c>
       <c r="G10">
         <v>5.44</v>
@@ -2205,28 +2205,28 @@
         <v>45.8</v>
       </c>
       <c r="M10">
-        <v>1.1130384</v>
+        <v>1.2521682</v>
       </c>
       <c r="N10">
-        <v>44.6869616</v>
+        <v>44.5478318</v>
       </c>
       <c r="O10">
-        <v>9.831131551999999</v>
+        <v>9.800522996</v>
       </c>
       <c r="P10">
-        <v>34.855830048</v>
+        <v>34.747308804</v>
       </c>
       <c r="Q10">
-        <v>51.455830048</v>
+        <v>51.347308804</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09118494647309017</v>
+        <v>0.09158092960309037</v>
       </c>
       <c r="T10">
-        <v>1.048151188754969</v>
+        <v>1.057296295683381</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>41.14862524060265</v>
+        <v>36.57655576942458</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2251,22 +2251,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08686970593881224</v>
+        <v>0.08671054112238151</v>
       </c>
       <c r="C11">
-        <v>252.5593157538479</v>
+        <v>250.3674991009802</v>
       </c>
       <c r="D11">
-        <v>272.0133157538479</v>
+        <v>272.5874991009802</v>
       </c>
       <c r="E11">
-        <v>-2.605999999999998</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="F11">
-        <v>24.894</v>
+        <v>27.66</v>
       </c>
       <c r="G11">
         <v>5.44</v>
@@ -2287,28 +2287,28 @@
         <v>45.8</v>
       </c>
       <c r="M11">
-        <v>1.2521682</v>
+        <v>1.391298</v>
       </c>
       <c r="N11">
-        <v>44.5478318</v>
+        <v>44.408702</v>
       </c>
       <c r="O11">
-        <v>9.800522996</v>
+        <v>9.769914439999999</v>
       </c>
       <c r="P11">
-        <v>34.747308804</v>
+        <v>34.63878756</v>
       </c>
       <c r="Q11">
-        <v>51.347308804</v>
+        <v>51.23878756</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09158092960309037</v>
+        <v>0.09198571235820169</v>
       </c>
       <c r="T11">
-        <v>1.057296295683381</v>
+        <v>1.066644627210201</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>36.57655576942458</v>
+        <v>32.91890019248213</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2333,22 +2333,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08671054112238151</v>
+        <v>0.08655137630595082</v>
       </c>
       <c r="C12">
-        <v>250.3674991009802</v>
+        <v>248.178111622662</v>
       </c>
       <c r="D12">
-        <v>272.5874991009802</v>
+        <v>273.164111622662</v>
       </c>
       <c r="E12">
-        <v>0.1600000000000037</v>
+        <v>2.926000000000002</v>
       </c>
       <c r="F12">
-        <v>27.66</v>
+        <v>30.426</v>
       </c>
       <c r="G12">
         <v>5.44</v>
@@ -2369,28 +2369,28 @@
         <v>45.8</v>
       </c>
       <c r="M12">
-        <v>1.391298</v>
+        <v>1.5304278</v>
       </c>
       <c r="N12">
-        <v>44.408702</v>
+        <v>44.2695722</v>
       </c>
       <c r="O12">
-        <v>9.769914439999999</v>
+        <v>9.739305884</v>
       </c>
       <c r="P12">
-        <v>34.63878756</v>
+        <v>34.530266316</v>
       </c>
       <c r="Q12">
-        <v>51.23878756</v>
+        <v>51.130266316</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09198571235820169</v>
+        <v>0.09239959135500092</v>
       </c>
       <c r="T12">
-        <v>1.066644627210201</v>
+        <v>1.076203033602793</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>32.91890019248213</v>
+        <v>29.92627290225648</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2415,22 +2415,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08655137630595082</v>
+        <v>0.0863922114895201</v>
       </c>
       <c r="C13">
-        <v>248.178111622662</v>
+        <v>245.9911687670893</v>
       </c>
       <c r="D13">
-        <v>273.164111622662</v>
+        <v>273.7431687670893</v>
       </c>
       <c r="E13">
-        <v>2.926000000000002</v>
+        <v>5.692</v>
       </c>
       <c r="F13">
-        <v>30.426</v>
+        <v>33.192</v>
       </c>
       <c r="G13">
         <v>5.44</v>
@@ -2451,28 +2451,28 @@
         <v>45.8</v>
       </c>
       <c r="M13">
-        <v>1.5304278</v>
+        <v>1.6695576</v>
       </c>
       <c r="N13">
-        <v>44.2695722</v>
+        <v>44.1304424</v>
       </c>
       <c r="O13">
-        <v>9.739305884</v>
+        <v>9.708697328</v>
       </c>
       <c r="P13">
-        <v>34.530266316</v>
+        <v>34.421745072</v>
       </c>
       <c r="Q13">
-        <v>51.130266316</v>
+        <v>51.021745072</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09239959135500092</v>
+        <v>0.09282287669263647</v>
       </c>
       <c r="T13">
-        <v>1.076203033602793</v>
+        <v>1.085978676504307</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>29.92627290225648</v>
+        <v>27.43241682706844</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0863922114895201</v>
+        <v>0.08623304667308937</v>
       </c>
       <c r="C14">
-        <v>245.9911687670893</v>
+        <v>243.8066861137251</v>
       </c>
       <c r="D14">
-        <v>273.7431687670893</v>
+        <v>274.3246861137251</v>
       </c>
       <c r="E14">
-        <v>5.692</v>
+        <v>8.458000000000006</v>
       </c>
       <c r="F14">
-        <v>33.192</v>
+        <v>35.95800000000001</v>
       </c>
       <c r="G14">
         <v>5.44</v>
@@ -2533,28 +2533,28 @@
         <v>45.8</v>
       </c>
       <c r="M14">
-        <v>1.6695576</v>
+        <v>1.8086874</v>
       </c>
       <c r="N14">
-        <v>44.1304424</v>
+        <v>43.9913126</v>
       </c>
       <c r="O14">
-        <v>9.708697328</v>
+        <v>9.678088772000001</v>
       </c>
       <c r="P14">
-        <v>34.421745072</v>
+        <v>34.313223828</v>
       </c>
       <c r="Q14">
-        <v>51.021745072</v>
+        <v>50.913223828</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09282287669263647</v>
+        <v>0.09325589272768894</v>
       </c>
       <c r="T14">
-        <v>1.085978676504307</v>
+        <v>1.095979046828844</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>27.43241682706844</v>
+        <v>25.32223091729394</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2579,22 +2579,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08623304667308937</v>
+        <v>0.08607388185665867</v>
       </c>
       <c r="C15">
-        <v>243.8066861137251</v>
+        <v>241.6246793746972</v>
       </c>
       <c r="D15">
-        <v>274.3246861137251</v>
+        <v>274.9086793746972</v>
       </c>
       <c r="E15">
-        <v>8.458000000000006</v>
+        <v>11.224</v>
       </c>
       <c r="F15">
-        <v>35.95800000000001</v>
+        <v>38.724</v>
       </c>
       <c r="G15">
         <v>5.44</v>
@@ -2615,28 +2615,28 @@
         <v>45.8</v>
       </c>
       <c r="M15">
-        <v>1.8086874</v>
+        <v>1.9478172</v>
       </c>
       <c r="N15">
-        <v>43.9913126</v>
+        <v>43.85218279999999</v>
       </c>
       <c r="O15">
-        <v>9.678088772000001</v>
+        <v>9.647480215999998</v>
       </c>
       <c r="P15">
-        <v>34.313223828</v>
+        <v>34.204702584</v>
       </c>
       <c r="Q15">
-        <v>50.913223828</v>
+        <v>50.804702584</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09325589272768894</v>
+        <v>0.09369897890309148</v>
       </c>
       <c r="T15">
-        <v>1.095979046828844</v>
+        <v>1.106211983905115</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>25.32223091729394</v>
+        <v>23.51350013748723</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2661,22 +2661,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08607388185665867</v>
+        <v>0.08591471704022796</v>
       </c>
       <c r="C16">
-        <v>241.6246793746972</v>
+        <v>239.4451643962131</v>
       </c>
       <c r="D16">
-        <v>274.9086793746972</v>
+        <v>275.4951643962131</v>
       </c>
       <c r="E16">
-        <v>11.224</v>
+        <v>13.99000000000001</v>
       </c>
       <c r="F16">
-        <v>38.724</v>
+        <v>41.49000000000001</v>
       </c>
       <c r="G16">
         <v>5.44</v>
@@ -2697,28 +2697,28 @@
         <v>45.8</v>
       </c>
       <c r="M16">
-        <v>1.9478172</v>
+        <v>2.086947</v>
       </c>
       <c r="N16">
-        <v>43.85218279999999</v>
+        <v>43.713053</v>
       </c>
       <c r="O16">
-        <v>9.647480215999998</v>
+        <v>9.616871659999999</v>
       </c>
       <c r="P16">
-        <v>34.204702584</v>
+        <v>34.09618133999999</v>
       </c>
       <c r="Q16">
-        <v>50.804702584</v>
+        <v>50.69618134</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09369897890309148</v>
+        <v>0.0941524906355623</v>
       </c>
       <c r="T16">
-        <v>1.106211983905115</v>
+        <v>1.116685695971416</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>23.51350013748723</v>
+        <v>21.94593346165475</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2743,22 +2743,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08591471704022796</v>
+        <v>0.08575555222379723</v>
       </c>
       <c r="C17">
-        <v>239.4451643962131</v>
+        <v>237.2681571599939</v>
       </c>
       <c r="D17">
-        <v>275.4951643962131</v>
+        <v>276.0841571599939</v>
       </c>
       <c r="E17">
-        <v>13.99</v>
+        <v>16.75600000000001</v>
       </c>
       <c r="F17">
-        <v>41.49</v>
+        <v>44.25600000000001</v>
       </c>
       <c r="G17">
         <v>5.44</v>
@@ -2779,28 +2779,28 @@
         <v>45.8</v>
       </c>
       <c r="M17">
-        <v>2.086947</v>
+        <v>2.2260768</v>
       </c>
       <c r="N17">
-        <v>43.713053</v>
+        <v>43.5739232</v>
       </c>
       <c r="O17">
-        <v>9.616871659999999</v>
+        <v>9.586263103999999</v>
       </c>
       <c r="P17">
-        <v>34.09618133999999</v>
+        <v>33.987660096</v>
       </c>
       <c r="Q17">
-        <v>50.69618134</v>
+        <v>50.587660096</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0941524906355623</v>
+        <v>0.09461680026642529</v>
       </c>
       <c r="T17">
-        <v>1.116685695971416</v>
+        <v>1.127408782134533</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>21.94593346165475</v>
+        <v>20.57431262030132</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2825,22 +2825,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08575555222379723</v>
+        <v>0.08559638740736651</v>
       </c>
       <c r="C18">
-        <v>237.2681571599939</v>
+        <v>235.0936737847249</v>
       </c>
       <c r="D18">
-        <v>276.0841571599939</v>
+        <v>276.6756737847249</v>
       </c>
       <c r="E18">
-        <v>16.75600000000001</v>
+        <v>19.52200000000001</v>
       </c>
       <c r="F18">
-        <v>44.25600000000001</v>
+        <v>47.02200000000001</v>
       </c>
       <c r="G18">
         <v>5.44</v>
@@ -2861,28 +2861,28 @@
         <v>45.8</v>
       </c>
       <c r="M18">
-        <v>2.2260768</v>
+        <v>2.3652066</v>
       </c>
       <c r="N18">
-        <v>43.5739232</v>
+        <v>43.4347934</v>
       </c>
       <c r="O18">
-        <v>9.586263103999999</v>
+        <v>9.555654548</v>
       </c>
       <c r="P18">
-        <v>33.987660096</v>
+        <v>33.879138852</v>
       </c>
       <c r="Q18">
-        <v>50.587660096</v>
+        <v>50.479138852</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09461680026642529</v>
+        <v>0.09509229808116448</v>
       </c>
       <c r="T18">
-        <v>1.127408782134533</v>
+        <v>1.138390255916039</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>20.57431262030132</v>
+        <v>19.36405893675419</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2907,22 +2907,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08559638740736651</v>
+        <v>0.08543722259093581</v>
       </c>
       <c r="C19">
-        <v>235.0936737847249</v>
+        <v>232.9217305275268</v>
       </c>
       <c r="D19">
-        <v>276.6756737847249</v>
+        <v>277.2697305275269</v>
       </c>
       <c r="E19">
-        <v>19.52200000000001</v>
+        <v>22.28800000000001</v>
       </c>
       <c r="F19">
-        <v>47.02200000000001</v>
+        <v>49.78800000000001</v>
       </c>
       <c r="G19">
         <v>5.44</v>
@@ -2943,28 +2943,28 @@
         <v>45.8</v>
       </c>
       <c r="M19">
-        <v>2.3652066</v>
+        <v>2.504336400000001</v>
       </c>
       <c r="N19">
-        <v>43.4347934</v>
+        <v>43.2956636</v>
       </c>
       <c r="O19">
-        <v>9.555654548</v>
+        <v>9.525045991999999</v>
       </c>
       <c r="P19">
-        <v>33.879138852</v>
+        <v>33.77061760799999</v>
       </c>
       <c r="Q19">
-        <v>50.479138852</v>
+        <v>50.370617608</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09509229808116448</v>
+        <v>0.09557939340358025</v>
       </c>
       <c r="T19">
-        <v>1.138390255916039</v>
+        <v>1.149639570521484</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>19.36405893675419</v>
+        <v>18.28827788471229</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2989,22 +2989,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08543722259093581</v>
+        <v>0.08527805777450509</v>
       </c>
       <c r="C20">
-        <v>232.9217305275268</v>
+        <v>230.7523437854453</v>
       </c>
       <c r="D20">
-        <v>277.2697305275269</v>
+        <v>277.8663437854453</v>
       </c>
       <c r="E20">
-        <v>22.288</v>
+        <v>25.054</v>
       </c>
       <c r="F20">
-        <v>49.788</v>
+        <v>52.554</v>
       </c>
       <c r="G20">
         <v>5.44</v>
@@ -3025,28 +3025,28 @@
         <v>45.8</v>
       </c>
       <c r="M20">
-        <v>2.5043364</v>
+        <v>2.6434662</v>
       </c>
       <c r="N20">
-        <v>43.2956636</v>
+        <v>43.1565338</v>
       </c>
       <c r="O20">
-        <v>9.525045991999999</v>
+        <v>9.494437436</v>
       </c>
       <c r="P20">
-        <v>33.77061760799999</v>
+        <v>33.662096364</v>
       </c>
       <c r="Q20">
-        <v>50.370617608</v>
+        <v>50.262096364</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09557939340358024</v>
+        <v>0.09607851577099394</v>
       </c>
       <c r="T20">
-        <v>1.149639570521484</v>
+        <v>1.161166645981385</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>18.28827788471229</v>
+        <v>17.32573694341165</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3071,22 +3071,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08527805777450509</v>
+        <v>0.08511889295807439</v>
       </c>
       <c r="C21">
-        <v>230.7523437854453</v>
+        <v>228.5855300969588</v>
       </c>
       <c r="D21">
-        <v>277.8663437854453</v>
+        <v>278.4655300969588</v>
       </c>
       <c r="E21">
-        <v>25.054</v>
+        <v>27.82000000000001</v>
       </c>
       <c r="F21">
-        <v>52.554</v>
+        <v>55.32000000000001</v>
       </c>
       <c r="G21">
         <v>5.44</v>
@@ -3107,28 +3107,28 @@
         <v>45.8</v>
       </c>
       <c r="M21">
-        <v>2.6434662</v>
+        <v>2.782596</v>
       </c>
       <c r="N21">
-        <v>43.1565338</v>
+        <v>43.017404</v>
       </c>
       <c r="O21">
-        <v>9.494437436</v>
+        <v>9.463828879999999</v>
       </c>
       <c r="P21">
-        <v>33.662096364</v>
+        <v>33.55357512</v>
       </c>
       <c r="Q21">
-        <v>50.262096364</v>
+        <v>50.15357512</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09607851577099394</v>
+        <v>0.09659011619759297</v>
       </c>
       <c r="T21">
-        <v>1.161166645981385</v>
+        <v>1.172981898327782</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>17.32573694341165</v>
+        <v>16.45945009624106</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3153,22 +3153,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08511889295807439</v>
+        <v>0.08495972814164368</v>
       </c>
       <c r="C22">
-        <v>228.5855300969588</v>
+        <v>226.4213061435075</v>
       </c>
       <c r="D22">
-        <v>278.4655300969588</v>
+        <v>279.0673061435075</v>
       </c>
       <c r="E22">
-        <v>27.82000000000001</v>
+        <v>30.58600000000001</v>
       </c>
       <c r="F22">
-        <v>55.32000000000001</v>
+        <v>58.08600000000001</v>
       </c>
       <c r="G22">
         <v>5.44</v>
@@ -3189,28 +3189,28 @@
         <v>45.8</v>
       </c>
       <c r="M22">
-        <v>2.782596</v>
+        <v>2.9217258</v>
       </c>
       <c r="N22">
-        <v>43.017404</v>
+        <v>42.8782742</v>
       </c>
       <c r="O22">
-        <v>9.463828879999999</v>
+        <v>9.433220324000001</v>
       </c>
       <c r="P22">
-        <v>33.55357512</v>
+        <v>33.445053876</v>
       </c>
       <c r="Q22">
-        <v>50.15357512</v>
+        <v>50.045053876</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09659011619759297</v>
+        <v>0.09711466853372616</v>
       </c>
       <c r="T22">
-        <v>1.172981898327782</v>
+        <v>1.185096270986747</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3227,7 +3227,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>16.45945009624106</v>
+        <v>15.67566675832482</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3235,22 +3235,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08495972814164365</v>
+        <v>0.08480056332521294</v>
       </c>
       <c r="C23">
-        <v>226.4213061435076</v>
+        <v>224.2596887510411</v>
       </c>
       <c r="D23">
-        <v>279.0673061435076</v>
+        <v>279.6716887510411</v>
       </c>
       <c r="E23">
-        <v>30.58600000000001</v>
+        <v>33.352</v>
       </c>
       <c r="F23">
-        <v>58.08600000000001</v>
+        <v>60.852</v>
       </c>
       <c r="G23">
         <v>5.44</v>
@@ -3271,28 +3271,28 @@
         <v>45.8</v>
       </c>
       <c r="M23">
-        <v>2.9217258</v>
+        <v>3.0608556</v>
       </c>
       <c r="N23">
-        <v>42.8782742</v>
+        <v>42.7391444</v>
       </c>
       <c r="O23">
-        <v>9.433220324000001</v>
+        <v>9.402611768</v>
       </c>
       <c r="P23">
-        <v>33.445053876</v>
+        <v>33.336532632</v>
       </c>
       <c r="Q23">
-        <v>50.045053876</v>
+        <v>49.936532632</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09711466853372613</v>
+        <v>0.09765267092976018</v>
       </c>
       <c r="T23">
-        <v>1.185096270986747</v>
+        <v>1.197521268585686</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3309,7 +3309,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.67566675832482</v>
+        <v>14.96313645112824</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3317,22 +3317,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08480056332521294</v>
+        <v>0.08464139850878223</v>
       </c>
       <c r="C24">
-        <v>224.2596887510411</v>
+        <v>222.1006948915867</v>
       </c>
       <c r="D24">
-        <v>279.6716887510411</v>
+        <v>280.2786948915867</v>
       </c>
       <c r="E24">
-        <v>33.352</v>
+        <v>36.11800000000001</v>
       </c>
       <c r="F24">
-        <v>60.852</v>
+        <v>63.61800000000001</v>
       </c>
       <c r="G24">
         <v>5.44</v>
@@ -3353,28 +3353,28 @@
         <v>45.8</v>
       </c>
       <c r="M24">
-        <v>3.0608556</v>
+        <v>3.1999854</v>
       </c>
       <c r="N24">
-        <v>42.7391444</v>
+        <v>42.60001459999999</v>
       </c>
       <c r="O24">
-        <v>9.402611768</v>
+        <v>9.372003211999999</v>
       </c>
       <c r="P24">
-        <v>33.336532632</v>
+        <v>33.228011388</v>
       </c>
       <c r="Q24">
-        <v>49.936532632</v>
+        <v>49.828011388</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09765267092976018</v>
+        <v>0.09820464741400289</v>
       </c>
       <c r="T24">
-        <v>1.197521268585686</v>
+        <v>1.210268993394986</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.96313645112824</v>
+        <v>14.31256530107918</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3399,22 +3399,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08464139850878223</v>
+        <v>0.08448223369235153</v>
       </c>
       <c r="C25">
-        <v>222.1006948915867</v>
+        <v>219.9443416848386</v>
       </c>
       <c r="D25">
-        <v>280.2786948915867</v>
+        <v>280.8883416848386</v>
       </c>
       <c r="E25">
-        <v>36.11800000000001</v>
+        <v>38.88400000000001</v>
       </c>
       <c r="F25">
-        <v>63.61800000000001</v>
+        <v>66.38400000000001</v>
       </c>
       <c r="G25">
         <v>5.44</v>
@@ -3435,28 +3435,28 @@
         <v>45.8</v>
       </c>
       <c r="M25">
-        <v>3.1999854</v>
+        <v>3.339115200000001</v>
       </c>
       <c r="N25">
-        <v>42.60001459999999</v>
+        <v>42.4608848</v>
       </c>
       <c r="O25">
-        <v>9.372003211999999</v>
+        <v>9.341394655999999</v>
       </c>
       <c r="P25">
-        <v>33.228011388</v>
+        <v>33.119490144</v>
       </c>
       <c r="Q25">
-        <v>49.828011388</v>
+        <v>49.719490144</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09820464741400289</v>
+        <v>0.09877114959519936</v>
       </c>
       <c r="T25">
-        <v>1.210268993394986</v>
+        <v>1.223352184646637</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.31256530107918</v>
+        <v>13.71620841353422</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3481,22 +3481,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08448223369235153</v>
+        <v>0.08432306887592081</v>
       </c>
       <c r="C26">
-        <v>219.9443416848386</v>
+        <v>217.7906463997664</v>
       </c>
       <c r="D26">
-        <v>280.8883416848386</v>
+        <v>281.5006463997664</v>
       </c>
       <c r="E26">
-        <v>38.884</v>
+        <v>41.65000000000001</v>
       </c>
       <c r="F26">
-        <v>66.384</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="G26">
         <v>5.44</v>
@@ -3517,28 +3517,28 @@
         <v>45.8</v>
       </c>
       <c r="M26">
-        <v>3.3391152</v>
+        <v>3.478245</v>
       </c>
       <c r="N26">
-        <v>42.4608848</v>
+        <v>42.321755</v>
       </c>
       <c r="O26">
-        <v>9.341394655999999</v>
+        <v>9.3107861</v>
       </c>
       <c r="P26">
-        <v>33.119490144</v>
+        <v>33.01096889999999</v>
       </c>
       <c r="Q26">
-        <v>49.719490144</v>
+        <v>49.6109689</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09877114959519936</v>
+        <v>0.09935275850122774</v>
       </c>
       <c r="T26">
-        <v>1.223352184646637</v>
+        <v>1.236784260998331</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>13.71620841353422</v>
+        <v>13.16756007699285</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08432306887592081</v>
+        <v>0.0844681040594901</v>
       </c>
       <c r="C27">
-        <v>217.7906463997664</v>
+        <v>214.4665904172055</v>
       </c>
       <c r="D27">
-        <v>281.5006463997664</v>
+        <v>280.9425904172055</v>
       </c>
       <c r="E27">
-        <v>41.65000000000001</v>
+        <v>44.41600000000001</v>
       </c>
       <c r="F27">
-        <v>69.15000000000001</v>
+        <v>71.91600000000001</v>
       </c>
       <c r="G27">
         <v>5.44</v>
@@ -3599,45 +3599,45 @@
         <v>45.8</v>
       </c>
       <c r="M27">
-        <v>3.478245</v>
+        <v>3.725248800000001</v>
       </c>
       <c r="N27">
-        <v>42.321755</v>
+        <v>42.07475119999999</v>
       </c>
       <c r="O27">
-        <v>9.3107861</v>
+        <v>9.256445263999998</v>
       </c>
       <c r="P27">
-        <v>33.01096889999999</v>
+        <v>32.81830593599999</v>
       </c>
       <c r="Q27">
-        <v>49.6109689</v>
+        <v>49.418305936</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09935275850122774</v>
+        <v>0.0999500865668785</v>
       </c>
       <c r="T27">
-        <v>1.236784260998331</v>
+        <v>1.250579366440612</v>
       </c>
       <c r="U27">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V27">
         <v>0.22</v>
       </c>
       <c r="W27">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y27">
-        <v>13.16756007699285</v>
+        <v>12.29448084111858</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3645,22 +3645,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0844681040594901</v>
+        <v>0.08432063924305937</v>
       </c>
       <c r="C28">
-        <v>214.4665904172055</v>
+        <v>212.2680138483472</v>
       </c>
       <c r="D28">
-        <v>280.9425904172055</v>
+        <v>281.5100138483472</v>
       </c>
       <c r="E28">
-        <v>44.41600000000001</v>
+        <v>47.18200000000002</v>
       </c>
       <c r="F28">
-        <v>71.91600000000001</v>
+        <v>74.68200000000002</v>
       </c>
       <c r="G28">
         <v>5.44</v>
@@ -3681,28 +3681,28 @@
         <v>45.8</v>
       </c>
       <c r="M28">
-        <v>3.725248800000001</v>
+        <v>3.868527600000001</v>
       </c>
       <c r="N28">
-        <v>42.07475119999999</v>
+        <v>41.9314724</v>
       </c>
       <c r="O28">
-        <v>9.256445263999998</v>
+        <v>9.224923927999999</v>
       </c>
       <c r="P28">
-        <v>32.81830593599999</v>
+        <v>32.70654847199999</v>
       </c>
       <c r="Q28">
-        <v>49.418305936</v>
+        <v>49.306548472</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0999500865668785</v>
+        <v>0.1005637797850128</v>
       </c>
       <c r="T28">
-        <v>1.250579366440612</v>
+        <v>1.264752419977202</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>12.29448084111858</v>
+        <v>11.83912969885493</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3727,22 +3727,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08432063924305937</v>
+        <v>0.08417317442662865</v>
       </c>
       <c r="C29">
-        <v>212.2680138483472</v>
+        <v>210.0717339832496</v>
       </c>
       <c r="D29">
-        <v>281.5100138483472</v>
+        <v>282.0797339832496</v>
       </c>
       <c r="E29">
-        <v>47.18200000000002</v>
+        <v>49.94800000000001</v>
       </c>
       <c r="F29">
-        <v>74.68200000000002</v>
+        <v>77.44800000000001</v>
       </c>
       <c r="G29">
         <v>5.44</v>
@@ -3763,28 +3763,28 @@
         <v>45.8</v>
       </c>
       <c r="M29">
-        <v>3.868527600000001</v>
+        <v>4.0118064</v>
       </c>
       <c r="N29">
-        <v>41.9314724</v>
+        <v>41.7881936</v>
       </c>
       <c r="O29">
-        <v>9.224923927999999</v>
+        <v>9.193402592</v>
       </c>
       <c r="P29">
-        <v>32.70654847199999</v>
+        <v>32.594791008</v>
       </c>
       <c r="Q29">
-        <v>49.306548472</v>
+        <v>49.194791008</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1005637797850128</v>
+        <v>0.1011945200369842</v>
       </c>
       <c r="T29">
-        <v>1.264752419977202</v>
+        <v>1.279319169445364</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.83912969885493</v>
+        <v>11.41630363818154</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3809,22 +3809,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08417317442662865</v>
+        <v>0.08402570961019795</v>
       </c>
       <c r="C30">
-        <v>210.0717339832496</v>
+        <v>207.8777647944015</v>
       </c>
       <c r="D30">
-        <v>282.0797339832496</v>
+        <v>282.6517647944015</v>
       </c>
       <c r="E30">
-        <v>49.94800000000001</v>
+        <v>52.71400000000001</v>
       </c>
       <c r="F30">
-        <v>77.44800000000001</v>
+        <v>80.21400000000001</v>
       </c>
       <c r="G30">
         <v>5.44</v>
@@ -3845,28 +3845,28 @@
         <v>45.8</v>
       </c>
       <c r="M30">
-        <v>4.0118064</v>
+        <v>4.1550852</v>
       </c>
       <c r="N30">
-        <v>41.7881936</v>
+        <v>41.6449148</v>
       </c>
       <c r="O30">
-        <v>9.193402592</v>
+        <v>9.161881255999999</v>
       </c>
       <c r="P30">
-        <v>32.594791008</v>
+        <v>32.48303354399999</v>
       </c>
       <c r="Q30">
-        <v>49.194791008</v>
+        <v>49.083033544</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1011945200369842</v>
+        <v>0.1018430276199971</v>
       </c>
       <c r="T30">
-        <v>1.279319169445364</v>
+        <v>1.29429624988446</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.41630363818154</v>
+        <v>11.02263799548563</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3891,22 +3891,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08402570961019795</v>
+        <v>0.08387824479376722</v>
       </c>
       <c r="C31">
-        <v>207.8777647944015</v>
+        <v>205.6861203678617</v>
       </c>
       <c r="D31">
-        <v>282.6517647944015</v>
+        <v>283.2261203678617</v>
       </c>
       <c r="E31">
-        <v>52.714</v>
+        <v>55.48</v>
       </c>
       <c r="F31">
-        <v>80.214</v>
+        <v>82.98</v>
       </c>
       <c r="G31">
         <v>5.44</v>
@@ -3927,28 +3927,28 @@
         <v>45.8</v>
       </c>
       <c r="M31">
-        <v>4.1550852</v>
+        <v>4.298364</v>
       </c>
       <c r="N31">
-        <v>41.6449148</v>
+        <v>41.501636</v>
       </c>
       <c r="O31">
-        <v>9.161881255999999</v>
+        <v>9.13035992</v>
       </c>
       <c r="P31">
-        <v>32.48303354399999</v>
+        <v>32.37127608</v>
       </c>
       <c r="Q31">
-        <v>49.083033544</v>
+        <v>48.97127608</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1018430276199971</v>
+        <v>0.102510063991096</v>
       </c>
       <c r="T31">
-        <v>1.29429624988446</v>
+        <v>1.30970124690753</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.02263799548563</v>
+        <v>10.65521672896944</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3973,22 +3973,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08387824479376722</v>
+        <v>0.08373077997733649</v>
       </c>
       <c r="C32">
-        <v>205.6861203678617</v>
+        <v>203.4968149044148</v>
       </c>
       <c r="D32">
-        <v>283.2261203678617</v>
+        <v>283.8028149044148</v>
       </c>
       <c r="E32">
-        <v>55.48</v>
+        <v>58.24600000000001</v>
       </c>
       <c r="F32">
-        <v>82.98</v>
+        <v>85.74600000000001</v>
       </c>
       <c r="G32">
         <v>5.44</v>
@@ -4009,28 +4009,28 @@
         <v>45.8</v>
       </c>
       <c r="M32">
-        <v>4.298364</v>
+        <v>4.4416428</v>
       </c>
       <c r="N32">
-        <v>41.501636</v>
+        <v>41.3583572</v>
       </c>
       <c r="O32">
-        <v>9.13035992</v>
+        <v>9.098838584000001</v>
       </c>
       <c r="P32">
-        <v>32.37127608</v>
+        <v>32.259518616</v>
       </c>
       <c r="Q32">
-        <v>48.97127608</v>
+        <v>48.859518616</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.102510063991096</v>
+        <v>0.1031964347497631</v>
       </c>
       <c r="T32">
-        <v>1.30970124690753</v>
+        <v>1.325552765583443</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.65521672896944</v>
+        <v>10.31150006029301</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4055,22 +4055,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08373077997733649</v>
+        <v>0.08358331516090579</v>
       </c>
       <c r="C33">
-        <v>203.4968149044148</v>
+        <v>201.3098627207421</v>
       </c>
       <c r="D33">
-        <v>283.8028149044148</v>
+        <v>284.3818627207421</v>
       </c>
       <c r="E33">
-        <v>58.24600000000001</v>
+        <v>61.01200000000001</v>
       </c>
       <c r="F33">
-        <v>85.74600000000001</v>
+        <v>88.51200000000001</v>
       </c>
       <c r="G33">
         <v>5.44</v>
@@ -4091,28 +4091,28 @@
         <v>45.8</v>
       </c>
       <c r="M33">
-        <v>4.4416428</v>
+        <v>4.5849216</v>
       </c>
       <c r="N33">
-        <v>41.3583572</v>
+        <v>41.2150784</v>
       </c>
       <c r="O33">
-        <v>9.098838584000001</v>
+        <v>9.067317247999998</v>
       </c>
       <c r="P33">
-        <v>32.259518616</v>
+        <v>32.147761152</v>
       </c>
       <c r="Q33">
-        <v>48.859518616</v>
+        <v>48.747761152</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1031964347497631</v>
+        <v>0.103902992883685</v>
       </c>
       <c r="T33">
-        <v>1.325552765583443</v>
+        <v>1.341870505396882</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.31150006029301</v>
+        <v>9.989265683408849</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4137,22 +4137,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08358331516090579</v>
+        <v>0.08387343034447507</v>
       </c>
       <c r="C34">
-        <v>201.3098627207421</v>
+        <v>197.4069113490147</v>
       </c>
       <c r="D34">
-        <v>284.3818627207421</v>
+        <v>283.2449113490147</v>
       </c>
       <c r="E34">
-        <v>61.01200000000001</v>
+        <v>63.77800000000001</v>
       </c>
       <c r="F34">
-        <v>88.51200000000001</v>
+        <v>91.27800000000001</v>
       </c>
       <c r="G34">
         <v>5.44</v>
@@ -4173,45 +4173,45 @@
         <v>45.8</v>
       </c>
       <c r="M34">
-        <v>4.5849216</v>
+        <v>4.883373000000001</v>
       </c>
       <c r="N34">
-        <v>41.2150784</v>
+        <v>40.916627</v>
       </c>
       <c r="O34">
-        <v>9.067317247999998</v>
+        <v>9.001657939999999</v>
       </c>
       <c r="P34">
-        <v>32.147761152</v>
+        <v>31.91496906</v>
       </c>
       <c r="Q34">
-        <v>48.747761152</v>
+        <v>48.51496906</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.103902992883685</v>
+        <v>0.1046306423051867</v>
       </c>
       <c r="T34">
-        <v>1.341870505396882</v>
+        <v>1.358675341921171</v>
       </c>
       <c r="U34">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V34">
         <v>0.22</v>
       </c>
       <c r="W34">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>9.989265683408849</v>
+        <v>9.378763407996889</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4219,22 +4219,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08387343034447507</v>
+        <v>0.08373922552804434</v>
       </c>
       <c r="C35">
-        <v>197.4069113490147</v>
+        <v>195.1657232751947</v>
       </c>
       <c r="D35">
-        <v>283.2449113490147</v>
+        <v>283.7697232751947</v>
       </c>
       <c r="E35">
-        <v>63.77800000000001</v>
+        <v>66.54400000000001</v>
       </c>
       <c r="F35">
-        <v>91.27800000000001</v>
+        <v>94.04400000000001</v>
       </c>
       <c r="G35">
         <v>5.44</v>
@@ -4255,28 +4255,28 @@
         <v>45.8</v>
       </c>
       <c r="M35">
-        <v>4.883373000000001</v>
+        <v>5.031354</v>
       </c>
       <c r="N35">
-        <v>40.916627</v>
+        <v>40.768646</v>
       </c>
       <c r="O35">
-        <v>9.001657939999999</v>
+        <v>8.969102119999999</v>
       </c>
       <c r="P35">
-        <v>31.91496906</v>
+        <v>31.79954388</v>
       </c>
       <c r="Q35">
-        <v>48.51496906</v>
+        <v>48.39954388</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1046306423051867</v>
+        <v>0.1053803417091581</v>
       </c>
       <c r="T35">
-        <v>1.358675341921171</v>
+        <v>1.375989415915892</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.378763407996889</v>
+        <v>9.102917425408746</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4301,22 +4301,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08373922552804434</v>
+        <v>0.08360502071161365</v>
       </c>
       <c r="C36">
-        <v>195.1657232751947</v>
+        <v>192.926483612955</v>
       </c>
       <c r="D36">
-        <v>283.7697232751947</v>
+        <v>284.296483612955</v>
       </c>
       <c r="E36">
-        <v>66.54400000000001</v>
+        <v>69.31000000000002</v>
       </c>
       <c r="F36">
-        <v>94.04400000000001</v>
+        <v>96.81000000000002</v>
       </c>
       <c r="G36">
         <v>5.44</v>
@@ -4337,28 +4337,28 @@
         <v>45.8</v>
       </c>
       <c r="M36">
-        <v>5.031354</v>
+        <v>5.179335000000001</v>
       </c>
       <c r="N36">
-        <v>40.768646</v>
+        <v>40.620665</v>
       </c>
       <c r="O36">
-        <v>8.969102119999999</v>
+        <v>8.9365463</v>
       </c>
       <c r="P36">
-        <v>31.79954388</v>
+        <v>31.6841187</v>
       </c>
       <c r="Q36">
-        <v>48.39954388</v>
+        <v>48.28411869999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1053803417091581</v>
+        <v>0.1061531087870979</v>
       </c>
       <c r="T36">
-        <v>1.375989415915892</v>
+        <v>1.393836230648913</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>9.102917425408746</v>
+        <v>8.842834070397066</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4383,22 +4383,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08360502071161365</v>
+        <v>0.08347081589518293</v>
       </c>
       <c r="C37">
-        <v>192.926483612955</v>
+        <v>190.6892032329553</v>
       </c>
       <c r="D37">
-        <v>284.296483612955</v>
+        <v>284.8252032329553</v>
       </c>
       <c r="E37">
-        <v>69.31000000000002</v>
+        <v>72.07600000000002</v>
       </c>
       <c r="F37">
-        <v>96.81000000000002</v>
+        <v>99.57600000000002</v>
       </c>
       <c r="G37">
         <v>5.44</v>
@@ -4419,28 +4419,28 @@
         <v>45.8</v>
       </c>
       <c r="M37">
-        <v>5.179335000000001</v>
+        <v>5.327316000000001</v>
       </c>
       <c r="N37">
-        <v>40.620665</v>
+        <v>40.47268399999999</v>
       </c>
       <c r="O37">
-        <v>8.9365463</v>
+        <v>8.903990479999999</v>
       </c>
       <c r="P37">
-        <v>31.6841187</v>
+        <v>31.56869352</v>
       </c>
       <c r="Q37">
-        <v>48.28411869999999</v>
+        <v>48.16869352</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1061531087870979</v>
+        <v>0.1069500248362233</v>
       </c>
       <c r="T37">
-        <v>1.393836230648913</v>
+        <v>1.412240758342341</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.842834070397066</v>
+        <v>8.597199790663813</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4465,22 +4465,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08347081589518293</v>
+        <v>0.08333661107875222</v>
       </c>
       <c r="C38">
-        <v>190.6892032329553</v>
+        <v>188.4538930868725</v>
       </c>
       <c r="D38">
-        <v>284.8252032329553</v>
+        <v>285.3558930868725</v>
       </c>
       <c r="E38">
-        <v>72.07600000000001</v>
+        <v>74.84200000000001</v>
       </c>
       <c r="F38">
-        <v>99.57600000000001</v>
+        <v>102.342</v>
       </c>
       <c r="G38">
         <v>5.44</v>
@@ -4501,28 +4501,28 @@
         <v>45.8</v>
       </c>
       <c r="M38">
-        <v>5.327316000000001</v>
+        <v>5.475297</v>
       </c>
       <c r="N38">
-        <v>40.47268399999999</v>
+        <v>40.324703</v>
       </c>
       <c r="O38">
-        <v>8.903990479999999</v>
+        <v>8.87143466</v>
       </c>
       <c r="P38">
-        <v>31.56869352</v>
+        <v>31.45326834</v>
       </c>
       <c r="Q38">
-        <v>48.16869352</v>
+        <v>48.05326834</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1069500248362233</v>
+        <v>0.1077722398075432</v>
       </c>
       <c r="T38">
-        <v>1.41224075834234</v>
+        <v>1.431229556756194</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4539,7 +4539,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.597199790663815</v>
+        <v>8.364843039564793</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4547,22 +4547,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08333661107875222</v>
+        <v>0.0832024062623215</v>
       </c>
       <c r="C39">
-        <v>188.4538930868725</v>
+        <v>186.220564208157</v>
       </c>
       <c r="D39">
-        <v>285.3558930868725</v>
+        <v>285.888564208157</v>
       </c>
       <c r="E39">
-        <v>74.84200000000001</v>
+        <v>77.608</v>
       </c>
       <c r="F39">
-        <v>102.342</v>
+        <v>105.108</v>
       </c>
       <c r="G39">
         <v>5.44</v>
@@ -4583,28 +4583,28 @@
         <v>45.8</v>
       </c>
       <c r="M39">
-        <v>5.475297</v>
+        <v>5.623278</v>
       </c>
       <c r="N39">
-        <v>40.324703</v>
+        <v>40.176722</v>
       </c>
       <c r="O39">
-        <v>8.87143466</v>
+        <v>8.83887884</v>
       </c>
       <c r="P39">
-        <v>31.45326834</v>
+        <v>31.33784316</v>
       </c>
       <c r="Q39">
-        <v>48.05326834</v>
+        <v>47.93784316</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1077722398075432</v>
+        <v>0.108620977842454</v>
       </c>
       <c r="T39">
-        <v>1.431229556756194</v>
+        <v>1.450830897054366</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4621,7 +4621,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.364843039564793</v>
+        <v>8.144715591155194</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0832024062623215</v>
+        <v>0.08306820144589078</v>
       </c>
       <c r="C40">
-        <v>186.220564208157</v>
+        <v>183.9892277127979</v>
       </c>
       <c r="D40">
-        <v>285.888564208157</v>
+        <v>286.4232277127979</v>
       </c>
       <c r="E40">
-        <v>77.608</v>
+        <v>80.37400000000001</v>
       </c>
       <c r="F40">
-        <v>105.108</v>
+        <v>107.874</v>
       </c>
       <c r="G40">
         <v>5.44</v>
@@ -4665,28 +4665,28 @@
         <v>45.8</v>
       </c>
       <c r="M40">
-        <v>5.623278</v>
+        <v>5.771259000000001</v>
       </c>
       <c r="N40">
-        <v>40.176722</v>
+        <v>40.028741</v>
       </c>
       <c r="O40">
-        <v>8.83887884</v>
+        <v>8.806323019999999</v>
       </c>
       <c r="P40">
-        <v>31.33784316</v>
+        <v>31.22241798</v>
       </c>
       <c r="Q40">
-        <v>47.93784316</v>
+        <v>47.82241798</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.108620977842454</v>
+        <v>0.1094975433539193</v>
       </c>
       <c r="T40">
-        <v>1.450830897054366</v>
+        <v>1.47107490424756</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.144715591155194</v>
+        <v>7.935876729843522</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4711,22 +4711,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08306820144589078</v>
+        <v>0.08293399662946008</v>
       </c>
       <c r="C41">
-        <v>183.9892277127979</v>
+        <v>181.7598948000951</v>
       </c>
       <c r="D41">
-        <v>286.4232277127979</v>
+        <v>286.9598948000951</v>
       </c>
       <c r="E41">
-        <v>80.37400000000001</v>
+        <v>83.14000000000001</v>
       </c>
       <c r="F41">
-        <v>107.874</v>
+        <v>110.64</v>
       </c>
       <c r="G41">
         <v>5.44</v>
@@ -4747,28 +4747,28 @@
         <v>45.8</v>
       </c>
       <c r="M41">
-        <v>5.771259000000001</v>
+        <v>5.91924</v>
       </c>
       <c r="N41">
-        <v>40.028741</v>
+        <v>39.88076</v>
       </c>
       <c r="O41">
-        <v>8.806323019999999</v>
+        <v>8.773767199999998</v>
       </c>
       <c r="P41">
-        <v>31.22241798</v>
+        <v>31.1069928</v>
       </c>
       <c r="Q41">
-        <v>47.82241798</v>
+        <v>47.70699279999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1094975433539193</v>
+        <v>0.1104033277157668</v>
       </c>
       <c r="T41">
-        <v>1.47107490424756</v>
+        <v>1.491993711680527</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.935876729843522</v>
+        <v>7.737479811597433</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4793,22 +4793,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08293399662946008</v>
+        <v>0.08305563181302936</v>
       </c>
       <c r="C42">
-        <v>181.7598948000951</v>
+        <v>178.5074067773095</v>
       </c>
       <c r="D42">
-        <v>286.9598948000951</v>
+        <v>286.4734067773095</v>
       </c>
       <c r="E42">
-        <v>83.14000000000001</v>
+        <v>85.90600000000002</v>
       </c>
       <c r="F42">
-        <v>110.64</v>
+        <v>113.406</v>
       </c>
       <c r="G42">
         <v>5.44</v>
@@ -4829,45 +4829,45 @@
         <v>45.8</v>
       </c>
       <c r="M42">
-        <v>5.91924</v>
+        <v>6.157945800000001</v>
       </c>
       <c r="N42">
-        <v>39.88076</v>
+        <v>39.6420542</v>
       </c>
       <c r="O42">
-        <v>8.773767199999998</v>
+        <v>8.721251923999999</v>
       </c>
       <c r="P42">
-        <v>31.1069928</v>
+        <v>30.920802276</v>
       </c>
       <c r="Q42">
-        <v>47.70699279999999</v>
+        <v>47.520802276</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1104033277157668</v>
+        <v>0.1113398166322531</v>
       </c>
       <c r="T42">
-        <v>1.491993711680527</v>
+        <v>1.513621631229865</v>
       </c>
       <c r="U42">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V42">
         <v>0.22</v>
       </c>
       <c r="W42">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y42">
-        <v>7.737479811597433</v>
+        <v>7.437545163193867</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4875,22 +4875,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08305563181302936</v>
+        <v>0.08292766699659863</v>
       </c>
       <c r="C43">
-        <v>178.5074067773095</v>
+        <v>176.2532558208869</v>
       </c>
       <c r="D43">
-        <v>286.4734067773095</v>
+        <v>286.9852558208869</v>
       </c>
       <c r="E43">
-        <v>85.90600000000002</v>
+        <v>88.67200000000003</v>
       </c>
       <c r="F43">
-        <v>113.406</v>
+        <v>116.172</v>
       </c>
       <c r="G43">
         <v>5.44</v>
@@ -4911,28 +4911,28 @@
         <v>45.8</v>
       </c>
       <c r="M43">
-        <v>6.157945800000001</v>
+        <v>6.308139600000001</v>
       </c>
       <c r="N43">
-        <v>39.6420542</v>
+        <v>39.49186039999999</v>
       </c>
       <c r="O43">
-        <v>8.721251923999999</v>
+        <v>8.688209287999998</v>
       </c>
       <c r="P43">
-        <v>30.920802276</v>
+        <v>30.803651112</v>
       </c>
       <c r="Q43">
-        <v>47.520802276</v>
+        <v>47.403651112</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1113398166322531</v>
+        <v>0.1123085982699976</v>
       </c>
       <c r="T43">
-        <v>1.513621631229865</v>
+        <v>1.535995341108491</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4949,7 +4949,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.437545163193867</v>
+        <v>7.260460754546394</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4957,22 +4957,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08292766699659865</v>
+        <v>0.08279970218016794</v>
       </c>
       <c r="C44">
-        <v>176.2532558208869</v>
+        <v>174.0009372047655</v>
       </c>
       <c r="D44">
-        <v>286.9852558208869</v>
+        <v>287.4989372047655</v>
       </c>
       <c r="E44">
-        <v>88.67200000000001</v>
+        <v>91.438</v>
       </c>
       <c r="F44">
-        <v>116.172</v>
+        <v>118.938</v>
       </c>
       <c r="G44">
         <v>5.44</v>
@@ -4993,28 +4993,28 @@
         <v>45.8</v>
       </c>
       <c r="M44">
-        <v>6.308139600000001</v>
+        <v>6.4583334</v>
       </c>
       <c r="N44">
-        <v>39.49186039999999</v>
+        <v>39.3416666</v>
       </c>
       <c r="O44">
-        <v>8.688209287999998</v>
+        <v>8.655166652</v>
       </c>
       <c r="P44">
-        <v>30.803651112</v>
+        <v>30.686499948</v>
       </c>
       <c r="Q44">
-        <v>47.403651112</v>
+        <v>47.286499948</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1123085982699976</v>
+        <v>0.1133113722459086</v>
       </c>
       <c r="T44">
-        <v>1.535995341108491</v>
+        <v>1.559154093438999</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -5031,7 +5031,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.260460754546394</v>
+        <v>7.09161283002206</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5039,22 +5039,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08279970218016794</v>
+        <v>0.08267173736373723</v>
       </c>
       <c r="C45">
-        <v>174.0009372047655</v>
+        <v>171.7504607858301</v>
       </c>
       <c r="D45">
-        <v>287.4989372047655</v>
+        <v>288.0144607858301</v>
       </c>
       <c r="E45">
-        <v>91.438</v>
+        <v>94.20400000000001</v>
       </c>
       <c r="F45">
-        <v>118.938</v>
+        <v>121.704</v>
       </c>
       <c r="G45">
         <v>5.44</v>
@@ -5075,28 +5075,28 @@
         <v>45.8</v>
       </c>
       <c r="M45">
-        <v>6.4583334</v>
+        <v>6.6085272</v>
       </c>
       <c r="N45">
-        <v>39.3416666</v>
+        <v>39.1914728</v>
       </c>
       <c r="O45">
-        <v>8.655166652</v>
+        <v>8.622124016000001</v>
       </c>
       <c r="P45">
-        <v>30.686499948</v>
+        <v>30.569348784</v>
       </c>
       <c r="Q45">
-        <v>47.286499948</v>
+        <v>47.169348784</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1133113722459086</v>
+        <v>0.1143499595781022</v>
       </c>
       <c r="T45">
-        <v>1.559154093438999</v>
+        <v>1.583139944067025</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5113,7 +5113,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.09161283002206</v>
+        <v>6.930439811157923</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5121,22 +5121,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08267173736373723</v>
+        <v>0.08254377254730649</v>
       </c>
       <c r="C46">
-        <v>171.7504607858301</v>
+        <v>169.5018364917913</v>
       </c>
       <c r="D46">
-        <v>288.0144607858301</v>
+        <v>288.5318364917914</v>
       </c>
       <c r="E46">
-        <v>94.20400000000001</v>
+        <v>96.97000000000001</v>
       </c>
       <c r="F46">
-        <v>121.704</v>
+        <v>124.47</v>
       </c>
       <c r="G46">
         <v>5.44</v>
@@ -5157,28 +5157,28 @@
         <v>45.8</v>
       </c>
       <c r="M46">
-        <v>6.6085272</v>
+        <v>6.758721</v>
       </c>
       <c r="N46">
-        <v>39.1914728</v>
+        <v>39.041279</v>
       </c>
       <c r="O46">
-        <v>8.622124016000001</v>
+        <v>8.58908138</v>
       </c>
       <c r="P46">
-        <v>30.569348784</v>
+        <v>30.45219762</v>
       </c>
       <c r="Q46">
-        <v>47.169348784</v>
+        <v>47.05219762</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1143499595781022</v>
+        <v>0.1154263137223754</v>
       </c>
       <c r="T46">
-        <v>1.583139944067025</v>
+        <v>1.607998007445161</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5195,7 +5195,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.930439811157923</v>
+        <v>6.776430037576636</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5203,22 +5203,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08254377254730649</v>
+        <v>0.0824158077308758</v>
       </c>
       <c r="C47">
-        <v>169.5018364917913</v>
+        <v>167.2550743218226</v>
       </c>
       <c r="D47">
-        <v>288.5318364917914</v>
+        <v>289.0510743218226</v>
       </c>
       <c r="E47">
-        <v>96.97000000000001</v>
+        <v>99.73600000000002</v>
       </c>
       <c r="F47">
-        <v>124.47</v>
+        <v>127.236</v>
       </c>
       <c r="G47">
         <v>5.44</v>
@@ -5239,28 +5239,28 @@
         <v>45.8</v>
       </c>
       <c r="M47">
-        <v>6.758721</v>
+        <v>6.908914800000001</v>
       </c>
       <c r="N47">
-        <v>39.041279</v>
+        <v>38.8910852</v>
       </c>
       <c r="O47">
-        <v>8.58908138</v>
+        <v>8.556038744</v>
       </c>
       <c r="P47">
-        <v>30.45219762</v>
+        <v>30.335046456</v>
       </c>
       <c r="Q47">
-        <v>47.05219762</v>
+        <v>46.935046456</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1154263137223754</v>
+        <v>0.1165425328349552</v>
       </c>
       <c r="T47">
-        <v>1.607998007445161</v>
+        <v>1.633776739837302</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.776430037576636</v>
+        <v>6.629116341107578</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5285,22 +5285,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0824158077308758</v>
+        <v>0.08228784291444508</v>
       </c>
       <c r="C48">
-        <v>167.2550743218226</v>
+        <v>165.0101843472051</v>
       </c>
       <c r="D48">
-        <v>289.0510743218226</v>
+        <v>289.5721843472051</v>
       </c>
       <c r="E48">
-        <v>99.73600000000002</v>
+        <v>102.502</v>
       </c>
       <c r="F48">
-        <v>127.236</v>
+        <v>130.002</v>
       </c>
       <c r="G48">
         <v>5.44</v>
@@ -5321,28 +5321,28 @@
         <v>45.8</v>
       </c>
       <c r="M48">
-        <v>6.908914800000001</v>
+        <v>7.059108600000001</v>
       </c>
       <c r="N48">
-        <v>38.8910852</v>
+        <v>38.7408914</v>
       </c>
       <c r="O48">
-        <v>8.556038744</v>
+        <v>8.522996107999999</v>
       </c>
       <c r="P48">
-        <v>30.335046456</v>
+        <v>30.21789529199999</v>
       </c>
       <c r="Q48">
-        <v>46.935046456</v>
+        <v>46.817895292</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1165425328349552</v>
+        <v>0.1177008734234813</v>
       </c>
       <c r="T48">
-        <v>1.633776739837302</v>
+        <v>1.660528254583863</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5359,7 +5359,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.629116341107578</v>
+        <v>6.488071312573374</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5367,22 +5367,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08228784291444508</v>
+        <v>0.08215987809801437</v>
       </c>
       <c r="C49">
-        <v>165.0101843472051</v>
+        <v>162.7671767119779</v>
       </c>
       <c r="D49">
-        <v>289.5721843472051</v>
+        <v>290.095176711978</v>
       </c>
       <c r="E49">
-        <v>102.502</v>
+        <v>105.268</v>
       </c>
       <c r="F49">
-        <v>130.002</v>
+        <v>132.768</v>
       </c>
       <c r="G49">
         <v>5.44</v>
@@ -5403,28 +5403,28 @@
         <v>45.8</v>
       </c>
       <c r="M49">
-        <v>7.059108600000001</v>
+        <v>7.209302400000002</v>
       </c>
       <c r="N49">
-        <v>38.7408914</v>
+        <v>38.5906976</v>
       </c>
       <c r="O49">
-        <v>8.522996107999999</v>
+        <v>8.489953472</v>
       </c>
       <c r="P49">
-        <v>30.21789529199999</v>
+        <v>30.100744128</v>
       </c>
       <c r="Q49">
-        <v>46.817895292</v>
+        <v>46.700744128</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1177008734234813</v>
+        <v>0.1189037655731045</v>
       </c>
       <c r="T49">
-        <v>1.660528254583863</v>
+        <v>1.688308673743754</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5441,7 +5441,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.488071312573374</v>
+        <v>6.352903160228094</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5449,22 +5449,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08215987809801437</v>
+        <v>0.08203191328158364</v>
       </c>
       <c r="C50">
-        <v>162.767176711978</v>
+        <v>160.5260616335972</v>
       </c>
       <c r="D50">
-        <v>290.095176711978</v>
+        <v>290.6200616335972</v>
       </c>
       <c r="E50">
-        <v>105.268</v>
+        <v>108.034</v>
       </c>
       <c r="F50">
-        <v>132.768</v>
+        <v>135.534</v>
       </c>
       <c r="G50">
         <v>5.44</v>
@@ -5485,28 +5485,28 @@
         <v>45.8</v>
       </c>
       <c r="M50">
-        <v>7.2093024</v>
+        <v>7.359496200000001</v>
       </c>
       <c r="N50">
-        <v>38.5906976</v>
+        <v>38.44050379999999</v>
       </c>
       <c r="O50">
-        <v>8.489953472</v>
+        <v>8.456910835999999</v>
       </c>
       <c r="P50">
-        <v>30.100744128</v>
+        <v>29.983592964</v>
       </c>
       <c r="Q50">
-        <v>46.700744128</v>
+        <v>46.583592964</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1189037655731045</v>
+        <v>0.1201538299638895</v>
       </c>
       <c r="T50">
-        <v>1.688308673743754</v>
+        <v>1.717178521105993</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.352903160228096</v>
+        <v>6.223252075325481</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5531,22 +5531,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08203191328158364</v>
+        <v>0.08229394846515292</v>
       </c>
       <c r="C51">
-        <v>160.5260616335972</v>
+        <v>156.6872780829459</v>
       </c>
       <c r="D51">
-        <v>290.6200616335972</v>
+        <v>289.5472780829459</v>
       </c>
       <c r="E51">
-        <v>108.034</v>
+        <v>110.8</v>
       </c>
       <c r="F51">
-        <v>135.534</v>
+        <v>138.3</v>
       </c>
       <c r="G51">
         <v>5.44</v>
@@ -5567,45 +5567,45 @@
         <v>45.8</v>
       </c>
       <c r="M51">
-        <v>7.359496200000001</v>
+        <v>7.647990000000001</v>
       </c>
       <c r="N51">
-        <v>38.44050379999999</v>
+        <v>38.15201</v>
       </c>
       <c r="O51">
-        <v>8.456910835999999</v>
+        <v>8.393442199999999</v>
       </c>
       <c r="P51">
-        <v>29.983592964</v>
+        <v>29.7585678</v>
       </c>
       <c r="Q51">
-        <v>46.583592964</v>
+        <v>46.3585678</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1201538299638895</v>
+        <v>0.1214538969303058</v>
       </c>
       <c r="T51">
-        <v>1.717178521105993</v>
+        <v>1.747203162362722</v>
       </c>
       <c r="U51">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V51">
         <v>0.22</v>
       </c>
       <c r="W51">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>6.223252075325481</v>
+        <v>5.988501554003077</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5613,22 +5613,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08229394846515292</v>
+        <v>0.08217378364872222</v>
       </c>
       <c r="C52">
-        <v>156.6872780829459</v>
+        <v>154.4122532372543</v>
       </c>
       <c r="D52">
-        <v>289.5472780829459</v>
+        <v>290.0382532372543</v>
       </c>
       <c r="E52">
-        <v>110.8</v>
+        <v>113.566</v>
       </c>
       <c r="F52">
-        <v>138.3</v>
+        <v>141.066</v>
       </c>
       <c r="G52">
         <v>5.44</v>
@@ -5649,28 +5649,28 @@
         <v>45.8</v>
       </c>
       <c r="M52">
-        <v>7.647990000000001</v>
+        <v>7.800949800000001</v>
       </c>
       <c r="N52">
-        <v>38.15201</v>
+        <v>37.9990502</v>
       </c>
       <c r="O52">
-        <v>8.393442199999999</v>
+        <v>8.359791044</v>
       </c>
       <c r="P52">
-        <v>29.7585678</v>
+        <v>29.639259156</v>
       </c>
       <c r="Q52">
-        <v>46.3585678</v>
+        <v>46.239259156</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1214538969303058</v>
+        <v>0.1228070278545351</v>
       </c>
       <c r="T52">
-        <v>1.747203162362722</v>
+        <v>1.77845329918095</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5687,7 +5687,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.988501554003077</v>
+        <v>5.871079954904978</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08217378364872222</v>
+        <v>0.08205361883229151</v>
       </c>
       <c r="C53">
-        <v>154.4122532372543</v>
+        <v>152.1388962784049</v>
       </c>
       <c r="D53">
-        <v>290.0382532372543</v>
+        <v>290.530896278405</v>
       </c>
       <c r="E53">
-        <v>113.566</v>
+        <v>116.332</v>
       </c>
       <c r="F53">
-        <v>141.066</v>
+        <v>143.832</v>
       </c>
       <c r="G53">
         <v>5.44</v>
@@ -5731,28 +5731,28 @@
         <v>45.8</v>
       </c>
       <c r="M53">
-        <v>7.800949800000001</v>
+        <v>7.953909600000001</v>
       </c>
       <c r="N53">
-        <v>37.9990502</v>
+        <v>37.84609039999999</v>
       </c>
       <c r="O53">
-        <v>8.359791044</v>
+        <v>8.326139887999998</v>
       </c>
       <c r="P53">
-        <v>29.639259156</v>
+        <v>29.51995051199999</v>
       </c>
       <c r="Q53">
-        <v>46.239259156</v>
+        <v>46.119950512</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1228070278545351</v>
+        <v>0.1242165392339406</v>
       </c>
       <c r="T53">
-        <v>1.77845329918095</v>
+        <v>1.811005525033271</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5769,7 +5769,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.871079954904978</v>
+        <v>5.758174571156804</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5777,22 +5777,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08205361883229151</v>
+        <v>0.08193345401586079</v>
       </c>
       <c r="C54">
-        <v>152.1388962784049</v>
+        <v>149.867215719801</v>
       </c>
       <c r="D54">
-        <v>290.530896278405</v>
+        <v>291.025215719801</v>
       </c>
       <c r="E54">
-        <v>116.332</v>
+        <v>119.098</v>
       </c>
       <c r="F54">
-        <v>143.832</v>
+        <v>146.598</v>
       </c>
       <c r="G54">
         <v>5.44</v>
@@ -5813,28 +5813,28 @@
         <v>45.8</v>
       </c>
       <c r="M54">
-        <v>7.953909600000001</v>
+        <v>8.106869400000001</v>
       </c>
       <c r="N54">
-        <v>37.84609039999999</v>
+        <v>37.6931306</v>
       </c>
       <c r="O54">
-        <v>8.326139887999998</v>
+        <v>8.292488731999999</v>
       </c>
       <c r="P54">
-        <v>29.51995051199999</v>
+        <v>29.400641868</v>
       </c>
       <c r="Q54">
-        <v>46.119950512</v>
+        <v>46.000641868</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1242165392339406</v>
+        <v>0.1256860298209804</v>
       </c>
       <c r="T54">
-        <v>1.811005525033271</v>
+        <v>1.844942951985691</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.758174571156804</v>
+        <v>5.649529767927431</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5859,22 +5859,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08193345401586079</v>
+        <v>0.08181328919943007</v>
       </c>
       <c r="C55">
-        <v>149.867215719801</v>
+        <v>147.5972201328844</v>
       </c>
       <c r="D55">
-        <v>291.025215719801</v>
+        <v>291.5212201328845</v>
       </c>
       <c r="E55">
-        <v>119.098</v>
+        <v>121.864</v>
       </c>
       <c r="F55">
-        <v>146.598</v>
+        <v>149.364</v>
       </c>
       <c r="G55">
         <v>5.44</v>
@@ -5895,28 +5895,28 @@
         <v>45.8</v>
       </c>
       <c r="M55">
-        <v>8.106869400000001</v>
+        <v>8.259829200000002</v>
       </c>
       <c r="N55">
-        <v>37.6931306</v>
+        <v>37.5401708</v>
       </c>
       <c r="O55">
-        <v>8.292488731999999</v>
+        <v>8.258837575999999</v>
       </c>
       <c r="P55">
-        <v>29.400641868</v>
+        <v>29.281333224</v>
       </c>
       <c r="Q55">
-        <v>46.000641868</v>
+        <v>45.881333224</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1256860298209804</v>
+        <v>0.1272194113031088</v>
       </c>
       <c r="T55">
-        <v>1.844942951985691</v>
+        <v>1.880355919240389</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.649529767927431</v>
+        <v>5.544908846299145</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5941,22 +5941,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08181328919943007</v>
+        <v>0.08169312438299935</v>
       </c>
       <c r="C56">
-        <v>147.5972201328844</v>
+        <v>145.3289181476315</v>
       </c>
       <c r="D56">
-        <v>291.5212201328845</v>
+        <v>292.0189181476316</v>
       </c>
       <c r="E56">
-        <v>121.864</v>
+        <v>124.63</v>
       </c>
       <c r="F56">
-        <v>149.364</v>
+        <v>152.13</v>
       </c>
       <c r="G56">
         <v>5.44</v>
@@ -5977,28 +5977,28 @@
         <v>45.8</v>
       </c>
       <c r="M56">
-        <v>8.259829200000002</v>
+        <v>8.412789000000002</v>
       </c>
       <c r="N56">
-        <v>37.5401708</v>
+        <v>37.38721099999999</v>
       </c>
       <c r="O56">
-        <v>8.258837575999999</v>
+        <v>8.225186419999998</v>
       </c>
       <c r="P56">
-        <v>29.281333224</v>
+        <v>29.16202457999999</v>
       </c>
       <c r="Q56">
-        <v>45.881333224</v>
+        <v>45.76202457999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1272194113031088</v>
+        <v>0.1288209430733319</v>
       </c>
       <c r="T56">
-        <v>1.880355919240389</v>
+        <v>1.917342796150852</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -6015,7 +6015,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.544908846299145</v>
+        <v>5.444092321820978</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6023,22 +6023,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08169312438299935</v>
+        <v>0.08157295956656863</v>
       </c>
       <c r="C57">
-        <v>145.3289181476315</v>
+        <v>143.0623184530532</v>
       </c>
       <c r="D57">
-        <v>292.0189181476316</v>
+        <v>292.5183184530532</v>
       </c>
       <c r="E57">
-        <v>124.63</v>
+        <v>127.396</v>
       </c>
       <c r="F57">
-        <v>152.13</v>
+        <v>154.896</v>
       </c>
       <c r="G57">
         <v>5.44</v>
@@ -6059,28 +6059,28 @@
         <v>45.8</v>
       </c>
       <c r="M57">
-        <v>8.412789000000002</v>
+        <v>8.565748800000001</v>
       </c>
       <c r="N57">
-        <v>37.38721099999999</v>
+        <v>37.2342512</v>
       </c>
       <c r="O57">
-        <v>8.225186419999998</v>
+        <v>8.191535263999999</v>
       </c>
       <c r="P57">
-        <v>29.16202457999999</v>
+        <v>29.042715936</v>
       </c>
       <c r="Q57">
-        <v>45.76202457999999</v>
+        <v>45.642715936</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1288209430733319</v>
+        <v>0.1304952717422014</v>
       </c>
       <c r="T57">
-        <v>1.917342796150852</v>
+        <v>1.956010894739064</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.444092321820978</v>
+        <v>5.346876387502747</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6105,22 +6105,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08157295956656863</v>
+        <v>0.08145279475013792</v>
       </c>
       <c r="C58">
-        <v>143.0623184530532</v>
+        <v>140.7974297977005</v>
       </c>
       <c r="D58">
-        <v>292.5183184530532</v>
+        <v>293.0194297977005</v>
       </c>
       <c r="E58">
-        <v>127.396</v>
+        <v>130.162</v>
       </c>
       <c r="F58">
-        <v>154.896</v>
+        <v>157.662</v>
       </c>
       <c r="G58">
         <v>5.44</v>
@@ -6141,28 +6141,28 @@
         <v>45.8</v>
       </c>
       <c r="M58">
-        <v>8.565748800000001</v>
+        <v>8.718708600000003</v>
       </c>
       <c r="N58">
-        <v>37.2342512</v>
+        <v>37.0812914</v>
       </c>
       <c r="O58">
-        <v>8.191535263999999</v>
+        <v>8.157884107999999</v>
       </c>
       <c r="P58">
-        <v>29.042715936</v>
+        <v>28.923407292</v>
       </c>
       <c r="Q58">
-        <v>45.642715936</v>
+        <v>45.523407292</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1304952717422014</v>
+        <v>0.1322474761631114</v>
       </c>
       <c r="T58">
-        <v>1.956010894739064</v>
+        <v>1.99647750954068</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6179,7 +6179,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.346876387502747</v>
+        <v>5.25307153859919</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6187,22 +6187,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08145279475013792</v>
+        <v>0.0813326299337072</v>
       </c>
       <c r="C59">
-        <v>140.7974297977005</v>
+        <v>138.5342609901762</v>
       </c>
       <c r="D59">
-        <v>293.0194297977005</v>
+        <v>293.5222609901762</v>
       </c>
       <c r="E59">
-        <v>130.162</v>
+        <v>132.928</v>
       </c>
       <c r="F59">
-        <v>157.662</v>
+        <v>160.428</v>
       </c>
       <c r="G59">
         <v>5.44</v>
@@ -6223,28 +6223,28 @@
         <v>45.8</v>
       </c>
       <c r="M59">
-        <v>8.718708600000003</v>
+        <v>8.871668400000003</v>
       </c>
       <c r="N59">
-        <v>37.0812914</v>
+        <v>36.92833159999999</v>
       </c>
       <c r="O59">
-        <v>8.157884107999999</v>
+        <v>8.124232951999998</v>
       </c>
       <c r="P59">
-        <v>28.923407292</v>
+        <v>28.80409864799999</v>
       </c>
       <c r="Q59">
-        <v>45.523407292</v>
+        <v>45.40409864799999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1322474761631114</v>
+        <v>0.1340831188897791</v>
       </c>
       <c r="T59">
-        <v>1.99647750954068</v>
+        <v>2.038871105999517</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.25307153859919</v>
+        <v>5.162501339657823</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6269,22 +6269,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08133262993370721</v>
+        <v>0.08121246511727648</v>
       </c>
       <c r="C60">
-        <v>138.5342609901762</v>
+        <v>136.2728208996501</v>
       </c>
       <c r="D60">
-        <v>293.5222609901762</v>
+        <v>294.0268208996501</v>
       </c>
       <c r="E60">
-        <v>132.928</v>
+        <v>135.694</v>
       </c>
       <c r="F60">
-        <v>160.428</v>
+        <v>163.194</v>
       </c>
       <c r="G60">
         <v>5.44</v>
@@ -6305,28 +6305,28 @@
         <v>45.8</v>
       </c>
       <c r="M60">
-        <v>8.871668400000001</v>
+        <v>9.0246282</v>
       </c>
       <c r="N60">
-        <v>36.92833159999999</v>
+        <v>36.77537179999999</v>
       </c>
       <c r="O60">
-        <v>8.124232951999998</v>
+        <v>8.090581795999999</v>
       </c>
       <c r="P60">
-        <v>28.80409864799999</v>
+        <v>28.684790004</v>
       </c>
       <c r="Q60">
-        <v>45.40409864799999</v>
+        <v>45.284790004</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1340831188897791</v>
+        <v>0.136008305164089</v>
       </c>
       <c r="T60">
-        <v>2.038871105999517</v>
+        <v>2.083332682773418</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6343,7 +6343,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.162501339657824</v>
+        <v>5.07500131695176</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6351,22 +6351,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08121246511727648</v>
+        <v>0.08109230030084577</v>
       </c>
       <c r="C61">
-        <v>136.2728208996501</v>
+        <v>134.0131184563807</v>
       </c>
       <c r="D61">
-        <v>294.0268208996501</v>
+        <v>294.5331184563807</v>
       </c>
       <c r="E61">
-        <v>135.694</v>
+        <v>138.46</v>
       </c>
       <c r="F61">
-        <v>163.194</v>
+        <v>165.96</v>
       </c>
       <c r="G61">
         <v>5.44</v>
@@ -6387,28 +6387,28 @@
         <v>45.8</v>
       </c>
       <c r="M61">
-        <v>9.0246282</v>
+        <v>9.177588</v>
       </c>
       <c r="N61">
-        <v>36.77537179999999</v>
+        <v>36.622412</v>
       </c>
       <c r="O61">
-        <v>8.090581795999999</v>
+        <v>8.056930639999999</v>
       </c>
       <c r="P61">
-        <v>28.684790004</v>
+        <v>28.56548136</v>
       </c>
       <c r="Q61">
-        <v>45.284790004</v>
+        <v>45.16548136</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.136008305164089</v>
+        <v>0.1380297507521144</v>
       </c>
       <c r="T61">
-        <v>2.083332682773418</v>
+        <v>2.130017338386015</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.07500131695176</v>
+        <v>4.990417961669231</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6433,22 +6433,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08109230030084577</v>
+        <v>0.08097213548441506</v>
       </c>
       <c r="C62">
-        <v>134.0131184563807</v>
+        <v>131.7551626522427</v>
       </c>
       <c r="D62">
-        <v>294.5331184563807</v>
+        <v>295.0411626522427</v>
       </c>
       <c r="E62">
-        <v>138.46</v>
+        <v>141.226</v>
       </c>
       <c r="F62">
-        <v>165.96</v>
+        <v>168.726</v>
       </c>
       <c r="G62">
         <v>5.44</v>
@@ -6469,28 +6469,28 @@
         <v>45.8</v>
       </c>
       <c r="M62">
-        <v>9.177588</v>
+        <v>9.3305478</v>
       </c>
       <c r="N62">
-        <v>36.622412</v>
+        <v>36.4694522</v>
       </c>
       <c r="O62">
-        <v>8.056930639999999</v>
+        <v>8.023279484</v>
       </c>
       <c r="P62">
-        <v>28.56548136</v>
+        <v>28.446172716</v>
       </c>
       <c r="Q62">
-        <v>45.16548136</v>
+        <v>45.046172716</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1380297507521144</v>
+        <v>0.1401548602164489</v>
       </c>
       <c r="T62">
-        <v>2.130017338386015</v>
+        <v>2.179096078901821</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6507,7 +6507,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.990417961669231</v>
+        <v>4.908607831150064</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6515,22 +6515,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08097213548441506</v>
+        <v>0.08085197066798434</v>
       </c>
       <c r="C63">
-        <v>131.7551626522427</v>
+        <v>129.4989625412584</v>
       </c>
       <c r="D63">
-        <v>295.0411626522427</v>
+        <v>295.5509625412584</v>
       </c>
       <c r="E63">
-        <v>141.226</v>
+        <v>143.992</v>
       </c>
       <c r="F63">
-        <v>168.726</v>
+        <v>171.492</v>
       </c>
       <c r="G63">
         <v>5.44</v>
@@ -6551,28 +6551,28 @@
         <v>45.8</v>
       </c>
       <c r="M63">
-        <v>9.3305478</v>
+        <v>9.483507600000001</v>
       </c>
       <c r="N63">
-        <v>36.4694522</v>
+        <v>36.31649239999999</v>
       </c>
       <c r="O63">
-        <v>8.023279484</v>
+        <v>7.989628327999998</v>
       </c>
       <c r="P63">
-        <v>28.446172716</v>
+        <v>28.326864072</v>
       </c>
       <c r="Q63">
-        <v>45.046172716</v>
+        <v>44.926864072</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1401548602164489</v>
+        <v>0.1423918175473272</v>
       </c>
       <c r="T63">
-        <v>2.179096078901821</v>
+        <v>2.230757911023724</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.908607831150064</v>
+        <v>4.829436737099256</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6597,22 +6597,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08085197066798434</v>
+        <v>0.08073180585155362</v>
       </c>
       <c r="C64">
-        <v>129.4989625412584</v>
+        <v>127.2445272401361</v>
       </c>
       <c r="D64">
-        <v>295.5509625412584</v>
+        <v>296.0625272401361</v>
       </c>
       <c r="E64">
-        <v>143.992</v>
+        <v>146.758</v>
       </c>
       <c r="F64">
-        <v>171.492</v>
+        <v>174.258</v>
       </c>
       <c r="G64">
         <v>5.44</v>
@@ -6633,28 +6633,28 @@
         <v>45.8</v>
       </c>
       <c r="M64">
-        <v>9.483507600000001</v>
+        <v>9.636467400000001</v>
       </c>
       <c r="N64">
-        <v>36.31649239999999</v>
+        <v>36.1635326</v>
       </c>
       <c r="O64">
-        <v>7.989628327999998</v>
+        <v>7.955977171999999</v>
       </c>
       <c r="P64">
-        <v>28.326864072</v>
+        <v>28.207555428</v>
       </c>
       <c r="Q64">
-        <v>44.926864072</v>
+        <v>44.807555428</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1423918175473272</v>
+        <v>0.1447496914906855</v>
       </c>
       <c r="T64">
-        <v>2.230757911023724</v>
+        <v>2.285212274611674</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.829436737099256</v>
+        <v>4.752779011113553</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6679,22 +6679,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08073180585155362</v>
+        <v>0.08061164103512292</v>
       </c>
       <c r="C65">
-        <v>127.2445272401361</v>
+        <v>124.9918659288134</v>
       </c>
       <c r="D65">
-        <v>296.0625272401361</v>
+        <v>296.5758659288134</v>
       </c>
       <c r="E65">
-        <v>146.758</v>
+        <v>149.524</v>
       </c>
       <c r="F65">
-        <v>174.258</v>
+        <v>177.024</v>
       </c>
       <c r="G65">
         <v>5.44</v>
@@ -6715,28 +6715,28 @@
         <v>45.8</v>
       </c>
       <c r="M65">
-        <v>9.636467400000001</v>
+        <v>9.789427200000002</v>
       </c>
       <c r="N65">
-        <v>36.1635326</v>
+        <v>36.01057279999999</v>
       </c>
       <c r="O65">
-        <v>7.955977171999999</v>
+        <v>7.922326015999998</v>
       </c>
       <c r="P65">
-        <v>28.207555428</v>
+        <v>28.08824678399999</v>
       </c>
       <c r="Q65">
-        <v>44.807555428</v>
+        <v>44.68824678399999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1447496914906855</v>
+        <v>0.147238558430897</v>
       </c>
       <c r="T65">
-        <v>2.285212274611674</v>
+        <v>2.342691880621178</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.752779011113553</v>
+        <v>4.678516839064903</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08061164103512292</v>
+        <v>0.08049147621869221</v>
       </c>
       <c r="C66">
-        <v>124.9918659288134</v>
+        <v>122.7409878510065</v>
       </c>
       <c r="D66">
-        <v>296.5758659288134</v>
+        <v>297.0909878510066</v>
       </c>
       <c r="E66">
-        <v>149.524</v>
+        <v>152.29</v>
       </c>
       <c r="F66">
-        <v>177.024</v>
+        <v>179.79</v>
       </c>
       <c r="G66">
         <v>5.44</v>
@@ -6797,28 +6797,28 @@
         <v>45.8</v>
       </c>
       <c r="M66">
-        <v>9.789427200000002</v>
+        <v>9.942387000000002</v>
       </c>
       <c r="N66">
-        <v>36.01057279999999</v>
+        <v>35.85761299999999</v>
       </c>
       <c r="O66">
-        <v>7.922326015999998</v>
+        <v>7.888674859999998</v>
       </c>
       <c r="P66">
-        <v>28.08824678399999</v>
+        <v>27.96893814</v>
       </c>
       <c r="Q66">
-        <v>44.68824678399999</v>
+        <v>44.56893814</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.147238558430897</v>
+        <v>0.1498696463391206</v>
       </c>
       <c r="T66">
-        <v>2.342691880621178</v>
+        <v>2.40345603554551</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.678516839064903</v>
+        <v>4.606539656925444</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6843,22 +6843,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08049147621869221</v>
+        <v>0.0803713114022615</v>
       </c>
       <c r="C67">
-        <v>122.7409878510065</v>
+        <v>120.4919023147649</v>
       </c>
       <c r="D67">
-        <v>297.0909878510066</v>
+        <v>297.6079023147649</v>
       </c>
       <c r="E67">
-        <v>152.29</v>
+        <v>155.056</v>
       </c>
       <c r="F67">
-        <v>179.79</v>
+        <v>182.556</v>
       </c>
       <c r="G67">
         <v>5.44</v>
@@ -6879,28 +6879,28 @@
         <v>45.8</v>
       </c>
       <c r="M67">
-        <v>9.942387000000002</v>
+        <v>10.0953468</v>
       </c>
       <c r="N67">
-        <v>35.85761299999999</v>
+        <v>35.7046532</v>
       </c>
       <c r="O67">
-        <v>7.888674859999998</v>
+        <v>7.855023703999999</v>
       </c>
       <c r="P67">
-        <v>27.96893814</v>
+        <v>27.849629496</v>
       </c>
       <c r="Q67">
-        <v>44.56893814</v>
+        <v>44.449629496</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1498696463391206</v>
+        <v>0.1526555041242985</v>
       </c>
       <c r="T67">
-        <v>2.40345603554551</v>
+        <v>2.467794552524215</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.606539656925444</v>
+        <v>4.536743601517482</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6925,22 +6925,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0803713114022615</v>
+        <v>0.08155764658583077</v>
       </c>
       <c r="C68">
-        <v>120.4919023147649</v>
+        <v>112.7000813367346</v>
       </c>
       <c r="D68">
-        <v>297.6079023147649</v>
+        <v>292.5820813367346</v>
       </c>
       <c r="E68">
-        <v>155.056</v>
+        <v>157.822</v>
       </c>
       <c r="F68">
-        <v>182.556</v>
+        <v>185.322</v>
       </c>
       <c r="G68">
         <v>5.44</v>
@@ -6961,45 +6961,45 @@
         <v>45.8</v>
       </c>
       <c r="M68">
-        <v>10.0953468</v>
+        <v>10.7116116</v>
       </c>
       <c r="N68">
-        <v>35.7046532</v>
+        <v>35.08838839999999</v>
       </c>
       <c r="O68">
-        <v>7.855023703999999</v>
+        <v>7.719445447999998</v>
       </c>
       <c r="P68">
-        <v>27.849629496</v>
+        <v>27.36894295199999</v>
       </c>
       <c r="Q68">
-        <v>44.449629496</v>
+        <v>43.96894295199999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1526555041242985</v>
+        <v>0.1556102017752448</v>
       </c>
       <c r="T68">
-        <v>2.467794552524215</v>
+        <v>2.536032373562235</v>
       </c>
       <c r="U68">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V68">
         <v>0.22</v>
       </c>
       <c r="W68">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y68">
-        <v>4.536743601517482</v>
+        <v>4.27573382141675</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7007,22 +7007,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08155764658583077</v>
+        <v>0.08145698176940006</v>
       </c>
       <c r="C69">
-        <v>112.7000813367346</v>
+        <v>110.3539402211637</v>
       </c>
       <c r="D69">
-        <v>292.5820813367346</v>
+        <v>293.0019402211637</v>
       </c>
       <c r="E69">
-        <v>157.822</v>
+        <v>160.588</v>
       </c>
       <c r="F69">
-        <v>185.322</v>
+        <v>188.088</v>
       </c>
       <c r="G69">
         <v>5.44</v>
@@ -7043,28 +7043,28 @@
         <v>45.8</v>
       </c>
       <c r="M69">
-        <v>10.7116116</v>
+        <v>10.8714864</v>
       </c>
       <c r="N69">
-        <v>35.08838839999999</v>
+        <v>34.9285136</v>
       </c>
       <c r="O69">
-        <v>7.719445447999998</v>
+        <v>7.684272991999999</v>
       </c>
       <c r="P69">
-        <v>27.36894295199999</v>
+        <v>27.244240608</v>
       </c>
       <c r="Q69">
-        <v>43.96894295199999</v>
+        <v>43.844240608</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1556102017752448</v>
+        <v>0.1587495680293752</v>
       </c>
       <c r="T69">
-        <v>2.536032373562235</v>
+        <v>2.608535058415132</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -7081,7 +7081,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.27573382141675</v>
+        <v>4.212855382866504</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7089,22 +7089,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08145698176940006</v>
+        <v>0.08135631695296934</v>
       </c>
       <c r="C70">
-        <v>110.3539402211637</v>
+        <v>108.0090058425991</v>
       </c>
       <c r="D70">
-        <v>293.0019402211637</v>
+        <v>293.4230058425991</v>
       </c>
       <c r="E70">
-        <v>160.588</v>
+        <v>163.354</v>
       </c>
       <c r="F70">
-        <v>188.088</v>
+        <v>190.854</v>
       </c>
       <c r="G70">
         <v>5.44</v>
@@ -7125,28 +7125,28 @@
         <v>45.8</v>
       </c>
       <c r="M70">
-        <v>10.8714864</v>
+        <v>11.0313612</v>
       </c>
       <c r="N70">
-        <v>34.9285136</v>
+        <v>34.76863879999999</v>
       </c>
       <c r="O70">
-        <v>7.684272991999999</v>
+        <v>7.649100535999998</v>
       </c>
       <c r="P70">
-        <v>27.244240608</v>
+        <v>27.11953826399999</v>
       </c>
       <c r="Q70">
-        <v>43.844240608</v>
+        <v>43.71953826399999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1587495680293752</v>
+        <v>0.1620914740418366</v>
       </c>
       <c r="T70">
-        <v>2.608535058415132</v>
+        <v>2.685715335839183</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.212855382866504</v>
+        <v>4.151799507752497</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7171,22 +7171,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08135631695296934</v>
+        <v>0.08125565213653863</v>
       </c>
       <c r="C71">
-        <v>108.0090058425991</v>
+        <v>105.6652834110409</v>
       </c>
       <c r="D71">
-        <v>293.4230058425991</v>
+        <v>293.8452834110409</v>
       </c>
       <c r="E71">
-        <v>163.354</v>
+        <v>166.12</v>
       </c>
       <c r="F71">
-        <v>190.854</v>
+        <v>193.62</v>
       </c>
       <c r="G71">
         <v>5.44</v>
@@ -7207,28 +7207,28 @@
         <v>45.8</v>
       </c>
       <c r="M71">
-        <v>11.0313612</v>
+        <v>11.191236</v>
       </c>
       <c r="N71">
-        <v>34.76863879999999</v>
+        <v>34.60876399999999</v>
       </c>
       <c r="O71">
-        <v>7.649100535999998</v>
+        <v>7.613928079999998</v>
       </c>
       <c r="P71">
-        <v>27.11953826399999</v>
+        <v>26.99483592</v>
       </c>
       <c r="Q71">
-        <v>43.71953826399999</v>
+        <v>43.59483591999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1620914740418366</v>
+        <v>0.1656561737884621</v>
       </c>
       <c r="T71">
-        <v>2.685715335839183</v>
+        <v>2.768040965091504</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.151799507752497</v>
+        <v>4.092488086213175</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7253,22 +7253,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08125565213653863</v>
+        <v>0.08115498732010791</v>
       </c>
       <c r="C72">
-        <v>105.6652834110409</v>
+        <v>103.3227781665243</v>
       </c>
       <c r="D72">
-        <v>293.8452834110409</v>
+        <v>294.2687781665243</v>
       </c>
       <c r="E72">
-        <v>166.12</v>
+        <v>168.886</v>
       </c>
       <c r="F72">
-        <v>193.62</v>
+        <v>196.386</v>
       </c>
       <c r="G72">
         <v>5.44</v>
@@ -7289,28 +7289,28 @@
         <v>45.8</v>
       </c>
       <c r="M72">
-        <v>11.191236</v>
+        <v>11.3511108</v>
       </c>
       <c r="N72">
-        <v>34.60876399999999</v>
+        <v>34.4488892</v>
       </c>
       <c r="O72">
-        <v>7.613928079999998</v>
+        <v>7.578755623999999</v>
       </c>
       <c r="P72">
-        <v>26.99483592</v>
+        <v>26.870133576</v>
       </c>
       <c r="Q72">
-        <v>43.59483591999999</v>
+        <v>43.47013357599999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1656561737884621</v>
+        <v>0.1694667148969239</v>
       </c>
       <c r="T72">
-        <v>2.768040965091504</v>
+        <v>2.856044223947434</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7327,7 +7327,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.092488086213175</v>
+        <v>4.034847408942567</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7335,22 +7335,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08115498732010792</v>
+        <v>0.08301992250367721</v>
       </c>
       <c r="C73">
-        <v>103.3227781665243</v>
+        <v>92.90405740977573</v>
       </c>
       <c r="D73">
-        <v>294.2687781665243</v>
+        <v>286.6160574097757</v>
       </c>
       <c r="E73">
-        <v>168.886</v>
+        <v>171.652</v>
       </c>
       <c r="F73">
-        <v>196.386</v>
+        <v>199.152</v>
       </c>
       <c r="G73">
         <v>5.44</v>
@@ -7371,45 +7371,45 @@
         <v>45.8</v>
       </c>
       <c r="M73">
-        <v>11.3511108</v>
+        <v>12.2080176</v>
       </c>
       <c r="N73">
-        <v>34.4488892</v>
+        <v>33.59198239999999</v>
       </c>
       <c r="O73">
-        <v>7.578755623999999</v>
+        <v>7.390236127999998</v>
       </c>
       <c r="P73">
-        <v>26.870133576</v>
+        <v>26.20174627199999</v>
       </c>
       <c r="Q73">
-        <v>43.47013357599999</v>
+        <v>42.801746272</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1694667148969238</v>
+        <v>0.1735494375131328</v>
       </c>
       <c r="T73">
-        <v>2.856044223947432</v>
+        <v>2.9503334298645</v>
       </c>
       <c r="U73">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V73">
         <v>0.22</v>
       </c>
       <c r="W73">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y73">
-        <v>4.034847408942568</v>
+        <v>3.751632861341876</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7417,22 +7417,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08301992250367721</v>
+        <v>0.08294655768724647</v>
       </c>
       <c r="C74">
-        <v>92.90405740977573</v>
+        <v>90.43157952084289</v>
       </c>
       <c r="D74">
-        <v>286.6160574097757</v>
+        <v>286.9095795208429</v>
       </c>
       <c r="E74">
-        <v>171.652</v>
+        <v>174.418</v>
       </c>
       <c r="F74">
-        <v>199.152</v>
+        <v>201.918</v>
       </c>
       <c r="G74">
         <v>5.44</v>
@@ -7453,28 +7453,28 @@
         <v>45.8</v>
       </c>
       <c r="M74">
-        <v>12.2080176</v>
+        <v>12.3775734</v>
       </c>
       <c r="N74">
-        <v>33.59198239999999</v>
+        <v>33.42242659999999</v>
       </c>
       <c r="O74">
-        <v>7.390236127999998</v>
+        <v>7.352933851999999</v>
       </c>
       <c r="P74">
-        <v>26.20174627199999</v>
+        <v>26.06949274799999</v>
       </c>
       <c r="Q74">
-        <v>42.801746272</v>
+        <v>42.669492748</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1735494375131328</v>
+        <v>0.1779345840268388</v>
       </c>
       <c r="T74">
-        <v>2.9503334298645</v>
+        <v>3.051607021405053</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7491,7 +7491,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.751632861341876</v>
+        <v>3.700240630364591</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7499,22 +7499,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08294655768724647</v>
+        <v>0.08287319287081577</v>
       </c>
       <c r="C75">
-        <v>90.43157952084289</v>
+        <v>87.95970343735002</v>
       </c>
       <c r="D75">
-        <v>286.9095795208429</v>
+        <v>287.20370343735</v>
       </c>
       <c r="E75">
-        <v>174.418</v>
+        <v>177.184</v>
       </c>
       <c r="F75">
-        <v>201.918</v>
+        <v>204.684</v>
       </c>
       <c r="G75">
         <v>5.44</v>
@@ -7535,28 +7535,28 @@
         <v>45.8</v>
       </c>
       <c r="M75">
-        <v>12.3775734</v>
+        <v>12.5471292</v>
       </c>
       <c r="N75">
-        <v>33.42242659999999</v>
+        <v>33.2528708</v>
       </c>
       <c r="O75">
-        <v>7.352933851999999</v>
+        <v>7.315631575999999</v>
       </c>
       <c r="P75">
-        <v>26.06949274799999</v>
+        <v>25.937239224</v>
       </c>
       <c r="Q75">
-        <v>42.669492748</v>
+        <v>42.537239224</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1779345840268388</v>
+        <v>0.1826570495031375</v>
       </c>
       <c r="T75">
-        <v>3.051607021405053</v>
+        <v>3.160670889217958</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7573,7 +7573,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.700240630364591</v>
+        <v>3.650237378602907</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7581,22 +7581,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08287319287081577</v>
+        <v>0.08279982805438504</v>
       </c>
       <c r="C76">
-        <v>87.95970343735002</v>
+        <v>85.48843101201012</v>
       </c>
       <c r="D76">
-        <v>287.20370343735</v>
+        <v>287.4984310120101</v>
       </c>
       <c r="E76">
-        <v>177.184</v>
+        <v>179.95</v>
       </c>
       <c r="F76">
-        <v>204.684</v>
+        <v>207.45</v>
       </c>
       <c r="G76">
         <v>5.44</v>
@@ -7617,28 +7617,28 @@
         <v>45.8</v>
       </c>
       <c r="M76">
-        <v>12.5471292</v>
+        <v>12.716685</v>
       </c>
       <c r="N76">
-        <v>33.2528708</v>
+        <v>33.083315</v>
       </c>
       <c r="O76">
-        <v>7.315631575999999</v>
+        <v>7.2783293</v>
       </c>
       <c r="P76">
-        <v>25.937239224</v>
+        <v>25.8049857</v>
       </c>
       <c r="Q76">
-        <v>42.537239224</v>
+        <v>42.4049857</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1826570495031375</v>
+        <v>0.1877573122175402</v>
       </c>
       <c r="T76">
-        <v>3.160670889217958</v>
+        <v>3.278459866455894</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.650237378602907</v>
+        <v>3.601567546888202</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7663,22 +7663,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08279982805438504</v>
+        <v>0.08272646323795434</v>
       </c>
       <c r="C77">
-        <v>85.48843101201012</v>
+        <v>83.01776410514861</v>
       </c>
       <c r="D77">
-        <v>287.4984310120101</v>
+        <v>287.7937641051486</v>
       </c>
       <c r="E77">
-        <v>179.95</v>
+        <v>182.716</v>
       </c>
       <c r="F77">
-        <v>207.45</v>
+        <v>210.216</v>
       </c>
       <c r="G77">
         <v>5.44</v>
@@ -7699,28 +7699,28 @@
         <v>45.8</v>
       </c>
       <c r="M77">
-        <v>12.716685</v>
+        <v>12.8862408</v>
       </c>
       <c r="N77">
-        <v>33.083315</v>
+        <v>32.91375919999999</v>
       </c>
       <c r="O77">
-        <v>7.2783293</v>
+        <v>7.241027023999998</v>
       </c>
       <c r="P77">
-        <v>25.8049857</v>
+        <v>25.672732176</v>
       </c>
       <c r="Q77">
-        <v>42.4049857</v>
+        <v>42.272732176</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1877573122175402</v>
+        <v>0.1932825968248097</v>
       </c>
       <c r="T77">
-        <v>3.278459866455894</v>
+        <v>3.406064591796992</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7737,7 +7737,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.601567546888202</v>
+        <v>3.55417850021862</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7745,22 +7745,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08272646323795434</v>
+        <v>0.0826530984215236</v>
       </c>
       <c r="C78">
-        <v>83.01776410514861</v>
+        <v>80.54770458474331</v>
       </c>
       <c r="D78">
-        <v>287.7937641051486</v>
+        <v>288.0897045847433</v>
       </c>
       <c r="E78">
-        <v>182.716</v>
+        <v>185.482</v>
       </c>
       <c r="F78">
-        <v>210.216</v>
+        <v>212.982</v>
       </c>
       <c r="G78">
         <v>5.44</v>
@@ -7781,28 +7781,28 @@
         <v>45.8</v>
       </c>
       <c r="M78">
-        <v>12.8862408</v>
+        <v>13.0557966</v>
       </c>
       <c r="N78">
-        <v>32.91375919999999</v>
+        <v>32.7442034</v>
       </c>
       <c r="O78">
-        <v>7.241027023999998</v>
+        <v>7.203724747999999</v>
       </c>
       <c r="P78">
-        <v>25.672732176</v>
+        <v>25.540478652</v>
       </c>
       <c r="Q78">
-        <v>42.272732176</v>
+        <v>42.140478652</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1932825968248097</v>
+        <v>0.1992883409631462</v>
       </c>
       <c r="T78">
-        <v>3.406064591796992</v>
+        <v>3.544765380211228</v>
       </c>
       <c r="U78">
         <v>0.0613</v>
@@ -7819,7 +7819,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.55417850021862</v>
+        <v>3.508020337878119</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7827,22 +7827,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0826530984215236</v>
+        <v>0.08428325360509291</v>
       </c>
       <c r="C79">
-        <v>80.54770458474331</v>
+        <v>71.34623280420075</v>
       </c>
       <c r="D79">
-        <v>288.0897045847433</v>
+        <v>281.6542328042008</v>
       </c>
       <c r="E79">
-        <v>185.482</v>
+        <v>188.248</v>
       </c>
       <c r="F79">
-        <v>212.982</v>
+        <v>215.748</v>
       </c>
       <c r="G79">
         <v>5.44</v>
@@ -7863,45 +7863,45 @@
         <v>45.8</v>
       </c>
       <c r="M79">
-        <v>13.0557966</v>
+        <v>13.8294468</v>
       </c>
       <c r="N79">
-        <v>32.7442034</v>
+        <v>31.9705532</v>
       </c>
       <c r="O79">
-        <v>7.203724747999999</v>
+        <v>7.033521703999999</v>
       </c>
       <c r="P79">
-        <v>25.540478652</v>
+        <v>24.937031496</v>
       </c>
       <c r="Q79">
-        <v>42.140478652</v>
+        <v>41.537031496</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1992883409631462</v>
+        <v>0.2058400618413314</v>
       </c>
       <c r="T79">
-        <v>3.544765380211228</v>
+        <v>3.696075331208578</v>
       </c>
       <c r="U79">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V79">
         <v>0.22</v>
       </c>
       <c r="W79">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y79">
-        <v>3.508020337878119</v>
+        <v>3.311773830316914</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7909,22 +7909,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08428325360509291</v>
+        <v>0.0842317287886622</v>
       </c>
       <c r="C80">
-        <v>71.34623280420075</v>
+        <v>68.7792374354764</v>
       </c>
       <c r="D80">
-        <v>281.6542328042008</v>
+        <v>281.8532374354764</v>
       </c>
       <c r="E80">
-        <v>188.248</v>
+        <v>191.014</v>
       </c>
       <c r="F80">
-        <v>215.748</v>
+        <v>218.514</v>
       </c>
       <c r="G80">
         <v>5.44</v>
@@ -7945,28 +7945,28 @@
         <v>45.8</v>
       </c>
       <c r="M80">
-        <v>13.8294468</v>
+        <v>14.0067474</v>
       </c>
       <c r="N80">
-        <v>31.9705532</v>
+        <v>31.7932526</v>
       </c>
       <c r="O80">
-        <v>7.033521703999999</v>
+        <v>6.994515571999999</v>
       </c>
       <c r="P80">
-        <v>24.937031496</v>
+        <v>24.798737028</v>
       </c>
       <c r="Q80">
-        <v>41.537031496</v>
+        <v>41.398737028</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2058400618413314</v>
+        <v>0.2130157561364866</v>
       </c>
       <c r="T80">
-        <v>3.696075331208578</v>
+        <v>3.861795753729484</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.311773830316914</v>
+        <v>3.269852642591383</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7991,22 +7991,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.0842317287886622</v>
+        <v>0.08418020397223148</v>
       </c>
       <c r="C81">
-        <v>68.7792374354764</v>
+        <v>66.21252348162238</v>
       </c>
       <c r="D81">
-        <v>281.8532374354764</v>
+        <v>282.0525234816224</v>
       </c>
       <c r="E81">
-        <v>191.014</v>
+        <v>193.78</v>
       </c>
       <c r="F81">
-        <v>218.514</v>
+        <v>221.28</v>
       </c>
       <c r="G81">
         <v>5.44</v>
@@ -8027,28 +8027,28 @@
         <v>45.8</v>
       </c>
       <c r="M81">
-        <v>14.0067474</v>
+        <v>14.184048</v>
       </c>
       <c r="N81">
-        <v>31.7932526</v>
+        <v>31.61595199999999</v>
       </c>
       <c r="O81">
-        <v>6.994515571999999</v>
+        <v>6.955509439999998</v>
       </c>
       <c r="P81">
-        <v>24.798737028</v>
+        <v>24.66044255999999</v>
       </c>
       <c r="Q81">
-        <v>41.398737028</v>
+        <v>41.26044255999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2130157561364866</v>
+        <v>0.2209090198611574</v>
       </c>
       <c r="T81">
-        <v>3.861795753729484</v>
+        <v>4.044088218502481</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -8065,7 +8065,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.269852642591383</v>
+        <v>3.228979484558991</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8073,22 +8073,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08418020397223148</v>
+        <v>0.08412867915580076</v>
       </c>
       <c r="C82">
-        <v>66.21252348162238</v>
+        <v>63.64609153998938</v>
       </c>
       <c r="D82">
-        <v>282.0525234816224</v>
+        <v>282.2520915399894</v>
       </c>
       <c r="E82">
-        <v>193.78</v>
+        <v>196.546</v>
       </c>
       <c r="F82">
-        <v>221.28</v>
+        <v>224.046</v>
       </c>
       <c r="G82">
         <v>5.44</v>
@@ -8109,28 +8109,28 @@
         <v>45.8</v>
       </c>
       <c r="M82">
-        <v>14.184048</v>
+        <v>14.3613486</v>
       </c>
       <c r="N82">
-        <v>31.61595199999999</v>
+        <v>31.43865139999999</v>
       </c>
       <c r="O82">
-        <v>6.955509439999998</v>
+        <v>6.916503307999998</v>
       </c>
       <c r="P82">
-        <v>24.66044255999999</v>
+        <v>24.52214809199999</v>
       </c>
       <c r="Q82">
-        <v>41.26044255999999</v>
+        <v>41.122148092</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2209090198611574</v>
+        <v>0.229633153451583</v>
       </c>
       <c r="T82">
-        <v>4.044088218502481</v>
+        <v>4.245569363777898</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8147,7 +8147,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.228979484558991</v>
+        <v>3.189115540305176</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8155,22 +8155,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08412867915580076</v>
+        <v>0.08407715433937005</v>
       </c>
       <c r="C83">
-        <v>63.64609153998938</v>
+        <v>61.07994220961976</v>
       </c>
       <c r="D83">
-        <v>282.2520915399894</v>
+        <v>282.4519422096198</v>
       </c>
       <c r="E83">
-        <v>196.546</v>
+        <v>199.312</v>
       </c>
       <c r="F83">
-        <v>224.046</v>
+        <v>226.812</v>
       </c>
       <c r="G83">
         <v>5.44</v>
@@ -8191,28 +8191,28 @@
         <v>45.8</v>
       </c>
       <c r="M83">
-        <v>14.3613486</v>
+        <v>14.5386492</v>
       </c>
       <c r="N83">
-        <v>31.43865139999999</v>
+        <v>31.2613508</v>
       </c>
       <c r="O83">
-        <v>6.916503307999998</v>
+        <v>6.877497175999999</v>
       </c>
       <c r="P83">
-        <v>24.52214809199999</v>
+        <v>24.383853624</v>
       </c>
       <c r="Q83">
-        <v>41.122148092</v>
+        <v>40.983853624</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.229633153451583</v>
+        <v>0.2393266352187225</v>
       </c>
       <c r="T83">
-        <v>4.245569363777898</v>
+        <v>4.469437302972807</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8229,7 +8229,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.189115540305176</v>
+        <v>3.150223887374625</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8237,22 +8237,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08407715433937005</v>
+        <v>0.08402562952293932</v>
       </c>
       <c r="C84">
-        <v>61.07994220961976</v>
+        <v>58.51407609125397</v>
       </c>
       <c r="D84">
-        <v>282.4519422096198</v>
+        <v>282.652076091254</v>
       </c>
       <c r="E84">
-        <v>199.312</v>
+        <v>202.078</v>
       </c>
       <c r="F84">
-        <v>226.812</v>
+        <v>229.578</v>
       </c>
       <c r="G84">
         <v>5.44</v>
@@ -8273,28 +8273,28 @@
         <v>45.8</v>
       </c>
       <c r="M84">
-        <v>14.5386492</v>
+        <v>14.7159498</v>
       </c>
       <c r="N84">
-        <v>31.2613508</v>
+        <v>31.08405019999999</v>
       </c>
       <c r="O84">
-        <v>6.877497175999999</v>
+        <v>6.838491043999999</v>
       </c>
       <c r="P84">
-        <v>24.383853624</v>
+        <v>24.245559156</v>
       </c>
       <c r="Q84">
-        <v>40.983853624</v>
+        <v>40.84555915599999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2393266352187225</v>
+        <v>0.2501605266055255</v>
       </c>
       <c r="T84">
-        <v>4.469437302972807</v>
+        <v>4.719642646778881</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8311,7 +8311,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.150223887374625</v>
+        <v>3.112269382707461</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8319,22 +8319,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08402562952293932</v>
+        <v>0.08397410470650862</v>
       </c>
       <c r="C85">
-        <v>58.51407609125397</v>
+        <v>55.94849378733596</v>
       </c>
       <c r="D85">
-        <v>282.652076091254</v>
+        <v>282.852493787336</v>
       </c>
       <c r="E85">
-        <v>202.078</v>
+        <v>204.8440000000001</v>
       </c>
       <c r="F85">
-        <v>229.578</v>
+        <v>232.3440000000001</v>
       </c>
       <c r="G85">
         <v>5.44</v>
@@ -8355,28 +8355,28 @@
         <v>45.8</v>
       </c>
       <c r="M85">
-        <v>14.7159498</v>
+        <v>14.8932504</v>
       </c>
       <c r="N85">
-        <v>31.08405019999999</v>
+        <v>30.90674959999999</v>
       </c>
       <c r="O85">
-        <v>6.838491043999999</v>
+        <v>6.799484911999998</v>
       </c>
       <c r="P85">
-        <v>24.245559156</v>
+        <v>24.10726468799999</v>
       </c>
       <c r="Q85">
-        <v>40.84555915599999</v>
+        <v>40.707264688</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2501605266055255</v>
+        <v>0.262348654415679</v>
       </c>
       <c r="T85">
-        <v>4.719642646778881</v>
+        <v>5.001123658560716</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8393,7 +8393,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.112269382707461</v>
+        <v>3.075218556722848</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8401,22 +8401,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08397410470650862</v>
+        <v>0.0839225798900779</v>
       </c>
       <c r="C86">
-        <v>55.94849378733599</v>
+        <v>53.38319590202008</v>
       </c>
       <c r="D86">
-        <v>282.852493787336</v>
+        <v>283.0531959020201</v>
       </c>
       <c r="E86">
-        <v>204.844</v>
+        <v>207.61</v>
       </c>
       <c r="F86">
-        <v>232.344</v>
+        <v>235.11</v>
       </c>
       <c r="G86">
         <v>5.44</v>
@@ -8437,28 +8437,28 @@
         <v>45.8</v>
       </c>
       <c r="M86">
-        <v>14.8932504</v>
+        <v>15.070551</v>
       </c>
       <c r="N86">
-        <v>30.90674959999999</v>
+        <v>30.729449</v>
       </c>
       <c r="O86">
-        <v>6.799484911999999</v>
+        <v>6.760478779999999</v>
       </c>
       <c r="P86">
-        <v>24.10726468799999</v>
+        <v>23.96897022</v>
       </c>
       <c r="Q86">
-        <v>40.707264688</v>
+        <v>40.56897022</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2623486544156788</v>
+        <v>0.2761618659338526</v>
       </c>
       <c r="T86">
-        <v>5.001123658560712</v>
+        <v>5.320135471913456</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8475,7 +8475,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.075218556722849</v>
+        <v>3.039039514879051</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8483,22 +8483,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.0839225798900779</v>
+        <v>0.08387105507364719</v>
       </c>
       <c r="C87">
-        <v>53.38319590202008</v>
+        <v>50.81818304117613</v>
       </c>
       <c r="D87">
-        <v>283.0531959020201</v>
+        <v>283.2541830411761</v>
       </c>
       <c r="E87">
-        <v>207.61</v>
+        <v>210.376</v>
       </c>
       <c r="F87">
-        <v>235.11</v>
+        <v>237.876</v>
       </c>
       <c r="G87">
         <v>5.44</v>
@@ -8519,28 +8519,28 @@
         <v>45.8</v>
       </c>
       <c r="M87">
-        <v>15.070551</v>
+        <v>15.2478516</v>
       </c>
       <c r="N87">
-        <v>30.729449</v>
+        <v>30.5521484</v>
       </c>
       <c r="O87">
-        <v>6.760478779999999</v>
+        <v>6.721472647999999</v>
       </c>
       <c r="P87">
-        <v>23.96897022</v>
+        <v>23.830675752</v>
       </c>
       <c r="Q87">
-        <v>40.56897022</v>
+        <v>40.430675752</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2761618659338526</v>
+        <v>0.2919483933831941</v>
       </c>
       <c r="T87">
-        <v>5.320135471913456</v>
+        <v>5.684720401459449</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8557,7 +8557,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.039039514879051</v>
+        <v>3.003701846101388</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8565,22 +8565,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08387105507364719</v>
+        <v>0.08911261025721648</v>
       </c>
       <c r="C88">
-        <v>50.81818304117613</v>
+        <v>28.96989174473643</v>
       </c>
       <c r="D88">
-        <v>283.2541830411761</v>
+        <v>264.1718917447365</v>
       </c>
       <c r="E88">
-        <v>210.376</v>
+        <v>213.142</v>
       </c>
       <c r="F88">
-        <v>237.876</v>
+        <v>240.642</v>
       </c>
       <c r="G88">
         <v>5.44</v>
@@ -8601,45 +8601,45 @@
         <v>45.8</v>
       </c>
       <c r="M88">
-        <v>15.2478516</v>
+        <v>17.3021598</v>
       </c>
       <c r="N88">
-        <v>30.5521484</v>
+        <v>28.4978402</v>
       </c>
       <c r="O88">
-        <v>6.721472647999999</v>
+        <v>6.269524843999999</v>
       </c>
       <c r="P88">
-        <v>23.830675752</v>
+        <v>22.228315356</v>
       </c>
       <c r="Q88">
-        <v>40.430675752</v>
+        <v>38.828315356</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2919483933831941</v>
+        <v>0.3101636173632036</v>
       </c>
       <c r="T88">
-        <v>5.684720401459449</v>
+        <v>6.105395320166365</v>
       </c>
       <c r="U88">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V88">
         <v>0.22</v>
       </c>
       <c r="W88">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y88">
-        <v>3.003701846101388</v>
+        <v>2.647068373510225</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8647,22 +8647,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08911261025721648</v>
+        <v>0.08912192544078576</v>
       </c>
       <c r="C89">
-        <v>28.96989174473643</v>
+        <v>26.1722675076212</v>
       </c>
       <c r="D89">
-        <v>264.1718917447365</v>
+        <v>264.1402675076212</v>
       </c>
       <c r="E89">
-        <v>213.142</v>
+        <v>215.908</v>
       </c>
       <c r="F89">
-        <v>240.642</v>
+        <v>243.408</v>
       </c>
       <c r="G89">
         <v>5.44</v>
@@ -8683,28 +8683,28 @@
         <v>45.8</v>
       </c>
       <c r="M89">
-        <v>17.3021598</v>
+        <v>17.5010352</v>
       </c>
       <c r="N89">
-        <v>28.4978402</v>
+        <v>28.29896479999999</v>
       </c>
       <c r="O89">
-        <v>6.269524843999999</v>
+        <v>6.225772255999998</v>
       </c>
       <c r="P89">
-        <v>22.228315356</v>
+        <v>22.07319254399999</v>
       </c>
       <c r="Q89">
-        <v>38.828315356</v>
+        <v>38.673192544</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3101636173632036</v>
+        <v>0.3314147120065479</v>
       </c>
       <c r="T89">
-        <v>6.105395320166365</v>
+        <v>6.596182725324434</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.647068373510225</v>
+        <v>2.616988051083972</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8729,22 +8729,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08912192544078576</v>
+        <v>0.08913124062435504</v>
       </c>
       <c r="C90">
-        <v>26.1722675076212</v>
+        <v>23.37465084112716</v>
       </c>
       <c r="D90">
-        <v>264.1402675076212</v>
+        <v>264.1086508411272</v>
       </c>
       <c r="E90">
-        <v>215.908</v>
+        <v>218.674</v>
       </c>
       <c r="F90">
-        <v>243.408</v>
+        <v>246.174</v>
       </c>
       <c r="G90">
         <v>5.44</v>
@@ -8765,28 +8765,28 @@
         <v>45.8</v>
       </c>
       <c r="M90">
-        <v>17.5010352</v>
+        <v>17.6999106</v>
       </c>
       <c r="N90">
-        <v>28.29896479999999</v>
+        <v>28.10008939999999</v>
       </c>
       <c r="O90">
-        <v>6.225772255999998</v>
+        <v>6.182019667999999</v>
       </c>
       <c r="P90">
-        <v>22.07319254399999</v>
+        <v>21.918069732</v>
       </c>
       <c r="Q90">
-        <v>38.673192544</v>
+        <v>38.518069732</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3314147120065479</v>
+        <v>0.3565296420395913</v>
       </c>
       <c r="T90">
-        <v>6.596182725324434</v>
+        <v>7.176204204147605</v>
       </c>
       <c r="U90">
         <v>0.07190000000000001</v>
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.616988051083972</v>
+        <v>2.587583690959433</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8811,22 +8811,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08913124062435504</v>
+        <v>0.08914055580792432</v>
       </c>
       <c r="C91">
-        <v>23.37465084112716</v>
+        <v>20.57704174253612</v>
       </c>
       <c r="D91">
-        <v>264.1086508411272</v>
+        <v>264.0770417425362</v>
       </c>
       <c r="E91">
-        <v>218.674</v>
+        <v>221.44</v>
       </c>
       <c r="F91">
-        <v>246.174</v>
+        <v>248.94</v>
       </c>
       <c r="G91">
         <v>5.44</v>
@@ -8847,28 +8847,28 @@
         <v>45.8</v>
       </c>
       <c r="M91">
-        <v>17.6999106</v>
+        <v>17.898786</v>
       </c>
       <c r="N91">
-        <v>28.10008939999999</v>
+        <v>27.90121399999999</v>
       </c>
       <c r="O91">
-        <v>6.182019667999999</v>
+        <v>6.138267079999999</v>
       </c>
       <c r="P91">
-        <v>21.918069732</v>
+        <v>21.76294691999999</v>
       </c>
       <c r="Q91">
-        <v>38.518069732</v>
+        <v>38.36294692</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3565296420395913</v>
+        <v>0.3866675580792432</v>
       </c>
       <c r="T91">
-        <v>7.176204204147605</v>
+        <v>7.872229978735412</v>
       </c>
       <c r="U91">
         <v>0.07190000000000001</v>
@@ -8885,7 +8885,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.587583690959433</v>
+        <v>2.558832761059883</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8893,22 +8893,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08914055580792432</v>
+        <v>0.08914987099149362</v>
       </c>
       <c r="C92">
-        <v>20.57704174253612</v>
+        <v>17.77944020913122</v>
       </c>
       <c r="D92">
-        <v>264.0770417425362</v>
+        <v>264.0454402091312</v>
       </c>
       <c r="E92">
-        <v>221.44</v>
+        <v>224.206</v>
       </c>
       <c r="F92">
-        <v>248.94</v>
+        <v>251.706</v>
       </c>
       <c r="G92">
         <v>5.44</v>
@@ -8929,28 +8929,28 @@
         <v>45.8</v>
       </c>
       <c r="M92">
-        <v>17.898786</v>
+        <v>18.0976614</v>
       </c>
       <c r="N92">
-        <v>27.90121399999999</v>
+        <v>27.70233859999999</v>
       </c>
       <c r="O92">
-        <v>6.138267079999999</v>
+        <v>6.094514491999998</v>
       </c>
       <c r="P92">
-        <v>21.76294691999999</v>
+        <v>21.607824108</v>
       </c>
       <c r="Q92">
-        <v>38.36294692</v>
+        <v>38.207824108</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3866675580792432</v>
+        <v>0.4235027887943735</v>
       </c>
       <c r="T92">
-        <v>7.872229978735412</v>
+        <v>8.722928147676065</v>
       </c>
       <c r="U92">
         <v>0.07190000000000001</v>
@@ -8967,7 +8967,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.558832761059883</v>
+        <v>2.530713719729555</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8975,22 +8975,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08914987099149362</v>
+        <v>0.0891591861750629</v>
       </c>
       <c r="C93">
-        <v>17.77944020913122</v>
+        <v>14.98184623819679</v>
       </c>
       <c r="D93">
-        <v>264.0454402091312</v>
+        <v>264.0138462381968</v>
       </c>
       <c r="E93">
-        <v>224.206</v>
+        <v>226.972</v>
       </c>
       <c r="F93">
-        <v>251.706</v>
+        <v>254.472</v>
       </c>
       <c r="G93">
         <v>5.44</v>
@@ -9011,28 +9011,28 @@
         <v>45.8</v>
       </c>
       <c r="M93">
-        <v>18.0976614</v>
+        <v>18.29653680000001</v>
       </c>
       <c r="N93">
-        <v>27.70233859999999</v>
+        <v>27.50346319999999</v>
       </c>
       <c r="O93">
-        <v>6.094514491999998</v>
+        <v>6.050761903999998</v>
       </c>
       <c r="P93">
-        <v>21.607824108</v>
+        <v>21.45270129599999</v>
       </c>
       <c r="Q93">
-        <v>38.207824108</v>
+        <v>38.052701296</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4235027887943735</v>
+        <v>0.4695468271882864</v>
       </c>
       <c r="T93">
-        <v>8.722928147676065</v>
+        <v>9.786300858851881</v>
       </c>
       <c r="U93">
         <v>0.07190000000000001</v>
@@ -9049,7 +9049,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.530713719729555</v>
+        <v>2.503205961906407</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9057,22 +9057,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.0891591861750629</v>
+        <v>0.09199756135863218</v>
       </c>
       <c r="C94">
-        <v>14.98184623819679</v>
+        <v>2.928780244116183</v>
       </c>
       <c r="D94">
-        <v>264.0138462381968</v>
+        <v>254.7267802441162</v>
       </c>
       <c r="E94">
-        <v>226.972</v>
+        <v>229.7380000000001</v>
       </c>
       <c r="F94">
-        <v>254.472</v>
+        <v>257.2380000000001</v>
       </c>
       <c r="G94">
         <v>5.44</v>
@@ -9093,45 +9093,45 @@
         <v>45.8</v>
       </c>
       <c r="M94">
-        <v>18.29653680000001</v>
+        <v>19.49864040000001</v>
       </c>
       <c r="N94">
-        <v>27.50346319999999</v>
+        <v>26.30135959999999</v>
       </c>
       <c r="O94">
-        <v>6.050761903999998</v>
+        <v>5.786299111999998</v>
       </c>
       <c r="P94">
-        <v>21.45270129599999</v>
+        <v>20.51506048799999</v>
       </c>
       <c r="Q94">
-        <v>38.052701296</v>
+        <v>37.115060488</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4695468271882864</v>
+        <v>0.528746305123317</v>
       </c>
       <c r="T94">
-        <v>9.786300858851881</v>
+        <v>11.15349434464936</v>
       </c>
       <c r="U94">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V94">
         <v>0.22</v>
       </c>
       <c r="W94">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y94">
-        <v>2.503205961906407</v>
+        <v>2.348881719978793</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9139,22 +9139,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09199756135863218</v>
+        <v>0.09203729654220147</v>
       </c>
       <c r="C95">
-        <v>2.928780244116183</v>
+        <v>0.03740319526821168</v>
       </c>
       <c r="D95">
-        <v>254.7267802441162</v>
+        <v>254.6014031952682</v>
       </c>
       <c r="E95">
-        <v>229.7380000000001</v>
+        <v>232.504</v>
       </c>
       <c r="F95">
-        <v>257.2380000000001</v>
+        <v>260.004</v>
       </c>
       <c r="G95">
         <v>5.44</v>
@@ -9175,28 +9175,28 @@
         <v>45.8</v>
       </c>
       <c r="M95">
-        <v>19.49864040000001</v>
+        <v>19.7083032</v>
       </c>
       <c r="N95">
-        <v>26.30135959999999</v>
+        <v>26.09169679999999</v>
       </c>
       <c r="O95">
-        <v>5.786299111999998</v>
+        <v>5.740173295999999</v>
       </c>
       <c r="P95">
-        <v>20.51506048799999</v>
+        <v>20.351523504</v>
       </c>
       <c r="Q95">
-        <v>37.115060488</v>
+        <v>36.95152350399999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.528746305123317</v>
+        <v>0.6076789423700248</v>
       </c>
       <c r="T95">
-        <v>11.15349434464936</v>
+        <v>12.97641899237933</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9213,7 +9213,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.348881719978793</v>
+        <v>2.323893616574764</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9221,22 +9221,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09203729654220147</v>
+        <v>0.09207703172577075</v>
       </c>
       <c r="C96">
-        <v>0.03740319526821168</v>
+        <v>-2.853850492612025</v>
       </c>
       <c r="D96">
-        <v>254.6014031952682</v>
+        <v>254.476149507388</v>
       </c>
       <c r="E96">
-        <v>232.504</v>
+        <v>235.27</v>
       </c>
       <c r="F96">
-        <v>260.004</v>
+        <v>262.77</v>
       </c>
       <c r="G96">
         <v>5.44</v>
@@ -9257,28 +9257,28 @@
         <v>45.8</v>
       </c>
       <c r="M96">
-        <v>19.7083032</v>
+        <v>19.917966</v>
       </c>
       <c r="N96">
-        <v>26.09169679999999</v>
+        <v>25.88203399999999</v>
       </c>
       <c r="O96">
-        <v>5.740173295999999</v>
+        <v>5.694047479999998</v>
       </c>
       <c r="P96">
-        <v>20.351523504</v>
+        <v>20.18798652</v>
       </c>
       <c r="Q96">
-        <v>36.95152350399999</v>
+        <v>36.78798652</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6076789423700248</v>
+        <v>0.7181846345154158</v>
       </c>
       <c r="T96">
-        <v>12.97641899237933</v>
+        <v>15.52851349920129</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.323893616574764</v>
+        <v>2.299431578505556</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9303,22 +9303,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09207703172577075</v>
+        <v>0.09211676690934004</v>
       </c>
       <c r="C97">
-        <v>-2.853850492612025</v>
+        <v>-5.744981001500946</v>
       </c>
       <c r="D97">
-        <v>254.476149507388</v>
+        <v>254.3510189984991</v>
       </c>
       <c r="E97">
-        <v>235.27</v>
+        <v>238.0360000000001</v>
       </c>
       <c r="F97">
-        <v>262.77</v>
+        <v>265.5360000000001</v>
       </c>
       <c r="G97">
         <v>5.44</v>
@@ -9339,28 +9339,28 @@
         <v>45.8</v>
       </c>
       <c r="M97">
-        <v>19.917966</v>
+        <v>20.12762880000001</v>
       </c>
       <c r="N97">
-        <v>25.88203399999999</v>
+        <v>25.67237119999999</v>
       </c>
       <c r="O97">
-        <v>5.694047479999998</v>
+        <v>5.647921663999997</v>
       </c>
       <c r="P97">
-        <v>20.18798652</v>
+        <v>20.02444953599999</v>
       </c>
       <c r="Q97">
-        <v>36.78798652</v>
+        <v>36.62444953599999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7181846345154158</v>
+        <v>0.8839431727335023</v>
       </c>
       <c r="T97">
-        <v>15.52851349920129</v>
+        <v>19.35665525943424</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9377,7 +9377,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.299431578505556</v>
+        <v>2.275479166229456</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9385,22 +9385,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09211676690934004</v>
+        <v>0.09215650209290932</v>
       </c>
       <c r="C98">
-        <v>-5.744981001500889</v>
+        <v>-8.635988513017253</v>
       </c>
       <c r="D98">
-        <v>254.3510189984991</v>
+        <v>254.2260114869828</v>
       </c>
       <c r="E98">
-        <v>238.036</v>
+        <v>240.802</v>
       </c>
       <c r="F98">
-        <v>265.536</v>
+        <v>268.302</v>
       </c>
       <c r="G98">
         <v>5.44</v>
@@ -9421,28 +9421,28 @@
         <v>45.8</v>
       </c>
       <c r="M98">
-        <v>20.1276288</v>
+        <v>20.3372916</v>
       </c>
       <c r="N98">
-        <v>25.6723712</v>
+        <v>25.46270839999999</v>
       </c>
       <c r="O98">
-        <v>5.647921663999999</v>
+        <v>5.601795847999998</v>
       </c>
       <c r="P98">
-        <v>20.024449536</v>
+        <v>19.86091255199999</v>
       </c>
       <c r="Q98">
-        <v>36.624449536</v>
+        <v>36.460912552</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8839431727335</v>
+        <v>1.160207403096976</v>
       </c>
       <c r="T98">
-        <v>19.35665525943418</v>
+        <v>25.73689152648906</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9459,7 +9459,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.275479166229457</v>
+        <v>2.252020618123998</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9467,22 +9467,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09215650209290932</v>
+        <v>0.0921962372764786</v>
       </c>
       <c r="C99">
-        <v>-8.635988513017253</v>
+        <v>-11.52687320842273</v>
       </c>
       <c r="D99">
-        <v>254.2260114869828</v>
+        <v>254.1011267915773</v>
       </c>
       <c r="E99">
-        <v>240.802</v>
+        <v>243.568</v>
       </c>
       <c r="F99">
-        <v>268.302</v>
+        <v>271.068</v>
       </c>
       <c r="G99">
         <v>5.44</v>
@@ -9503,28 +9503,28 @@
         <v>45.8</v>
       </c>
       <c r="M99">
-        <v>20.3372916</v>
+        <v>20.5469544</v>
       </c>
       <c r="N99">
-        <v>25.46270839999999</v>
+        <v>25.25304559999999</v>
       </c>
       <c r="O99">
-        <v>5.601795847999998</v>
+        <v>5.555670031999998</v>
       </c>
       <c r="P99">
-        <v>19.86091255199999</v>
+        <v>19.69737556799999</v>
       </c>
       <c r="Q99">
-        <v>36.460912552</v>
+        <v>36.29737556799999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.160207403096976</v>
+        <v>1.712735863823929</v>
       </c>
       <c r="T99">
-        <v>25.73689152648906</v>
+        <v>38.49736406059882</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9541,7 +9541,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.252020618123998</v>
+        <v>2.229040815898243</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9549,22 +9549,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.0921962372764786</v>
+        <v>0.09223597246004789</v>
       </c>
       <c r="C100">
-        <v>-11.52687320842273</v>
+        <v>-14.4176352686232</v>
       </c>
       <c r="D100">
-        <v>254.1011267915773</v>
+        <v>253.9763647313768</v>
       </c>
       <c r="E100">
-        <v>243.568</v>
+        <v>246.334</v>
       </c>
       <c r="F100">
-        <v>271.068</v>
+        <v>273.834</v>
       </c>
       <c r="G100">
         <v>5.44</v>
@@ -9585,28 +9585,28 @@
         <v>45.8</v>
       </c>
       <c r="M100">
-        <v>20.5469544</v>
+        <v>20.7566172</v>
       </c>
       <c r="N100">
-        <v>25.25304559999999</v>
+        <v>25.0433828</v>
       </c>
       <c r="O100">
-        <v>5.555670031999998</v>
+        <v>5.509544215999999</v>
       </c>
       <c r="P100">
-        <v>19.69737556799999</v>
+        <v>19.533838584</v>
       </c>
       <c r="Q100">
-        <v>36.29737556799999</v>
+        <v>36.133838584</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.712735863823929</v>
+        <v>3.370321246004786</v>
       </c>
       <c r="T100">
-        <v>38.49736406059882</v>
+        <v>76.7787816629281</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9623,91 +9623,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.229040815898243</v>
+        <v>2.206525252101291</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09223597246004789</v>
-      </c>
-      <c r="C101">
-        <v>-14.4176352686232</v>
-      </c>
-      <c r="D101">
-        <v>253.9763647313768</v>
-      </c>
-      <c r="E101">
-        <v>246.334</v>
-      </c>
-      <c r="F101">
-        <v>273.834</v>
-      </c>
-      <c r="G101">
-        <v>5.44</v>
-      </c>
-      <c r="H101">
-        <v>249.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>62.4</v>
-      </c>
-      <c r="K101">
-        <v>16.6</v>
-      </c>
-      <c r="L101">
-        <v>45.8</v>
-      </c>
-      <c r="M101">
-        <v>20.7566172</v>
-      </c>
-      <c r="N101">
-        <v>25.0433828</v>
-      </c>
-      <c r="O101">
-        <v>5.509544215999999</v>
-      </c>
-      <c r="P101">
-        <v>19.533838584</v>
-      </c>
-      <c r="Q101">
-        <v>36.133838584</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.370321246004786</v>
-      </c>
-      <c r="T101">
-        <v>76.7787816629281</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.22</v>
-      </c>
-      <c r="W101">
-        <v>0.05912400000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.206525252101291</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
